--- a/data/boe/boe_mpr.xlsx
+++ b/data/boe/boe_mpr.xlsx
@@ -467,40 +467,140 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE7"/>
+  <dimension ref="A1:EA18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="21" customWidth="1" min="20" max="20"/>
-    <col width="15" customWidth="1" min="21" max="21"/>
-    <col width="11" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="24" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="11" customWidth="1" min="30" max="30"/>
-    <col width="10" customWidth="1" min="31" max="31"/>
+    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="11" customWidth="1" min="32" max="32"/>
+    <col width="11" customWidth="1" min="33" max="33"/>
+    <col width="11" customWidth="1" min="34" max="34"/>
+    <col width="11" customWidth="1" min="35" max="35"/>
+    <col width="11" customWidth="1" min="36" max="36"/>
+    <col width="11" customWidth="1" min="37" max="37"/>
+    <col width="11" customWidth="1" min="38" max="38"/>
+    <col width="11" customWidth="1" min="39" max="39"/>
+    <col width="11" customWidth="1" min="40" max="40"/>
+    <col width="11" customWidth="1" min="41" max="41"/>
+    <col width="11" customWidth="1" min="42" max="42"/>
+    <col width="11" customWidth="1" min="43" max="43"/>
+    <col width="11" customWidth="1" min="44" max="44"/>
+    <col width="11" customWidth="1" min="45" max="45"/>
+    <col width="11" customWidth="1" min="46" max="46"/>
+    <col width="11" customWidth="1" min="47" max="47"/>
+    <col width="10" customWidth="1" min="48" max="48"/>
+    <col width="10" customWidth="1" min="49" max="49"/>
+    <col width="10" customWidth="1" min="50" max="50"/>
+    <col width="11" customWidth="1" min="51" max="51"/>
+    <col width="10" customWidth="1" min="52" max="52"/>
+    <col width="10" customWidth="1" min="53" max="53"/>
+    <col width="17" customWidth="1" min="54" max="54"/>
+    <col width="10" customWidth="1" min="55" max="55"/>
+    <col width="10" customWidth="1" min="56" max="56"/>
+    <col width="10" customWidth="1" min="57" max="57"/>
+    <col width="10" customWidth="1" min="58" max="58"/>
+    <col width="10" customWidth="1" min="59" max="59"/>
+    <col width="11" customWidth="1" min="60" max="60"/>
+    <col width="11" customWidth="1" min="61" max="61"/>
+    <col width="11" customWidth="1" min="62" max="62"/>
+    <col width="11" customWidth="1" min="63" max="63"/>
+    <col width="11" customWidth="1" min="64" max="64"/>
+    <col width="11" customWidth="1" min="65" max="65"/>
+    <col width="11" customWidth="1" min="66" max="66"/>
+    <col width="11" customWidth="1" min="67" max="67"/>
+    <col width="11" customWidth="1" min="68" max="68"/>
+    <col width="11" customWidth="1" min="69" max="69"/>
+    <col width="10" customWidth="1" min="70" max="70"/>
+    <col width="11" customWidth="1" min="71" max="71"/>
+    <col width="11" customWidth="1" min="72" max="72"/>
+    <col width="11" customWidth="1" min="73" max="73"/>
+    <col width="10" customWidth="1" min="74" max="74"/>
+    <col width="10" customWidth="1" min="75" max="75"/>
+    <col width="11" customWidth="1" min="76" max="76"/>
+    <col width="11" customWidth="1" min="77" max="77"/>
+    <col width="10" customWidth="1" min="78" max="78"/>
+    <col width="10" customWidth="1" min="79" max="79"/>
+    <col width="21" customWidth="1" min="80" max="80"/>
+    <col width="10" customWidth="1" min="81" max="81"/>
+    <col width="14" customWidth="1" min="82" max="82"/>
+    <col width="11" customWidth="1" min="83" max="83"/>
+    <col width="14" customWidth="1" min="84" max="84"/>
+    <col width="10" customWidth="1" min="85" max="85"/>
+    <col width="10" customWidth="1" min="86" max="86"/>
+    <col width="15" customWidth="1" min="87" max="87"/>
+    <col width="15" customWidth="1" min="88" max="88"/>
+    <col width="14" customWidth="1" min="89" max="89"/>
+    <col width="15" customWidth="1" min="90" max="90"/>
+    <col width="11" customWidth="1" min="91" max="91"/>
+    <col width="15" customWidth="1" min="92" max="92"/>
+    <col width="10" customWidth="1" min="93" max="93"/>
+    <col width="13" customWidth="1" min="94" max="94"/>
+    <col width="14" customWidth="1" min="95" max="95"/>
+    <col width="10" customWidth="1" min="96" max="96"/>
+    <col width="11" customWidth="1" min="97" max="97"/>
+    <col width="13" customWidth="1" min="98" max="98"/>
+    <col width="14" customWidth="1" min="99" max="99"/>
+    <col width="11" customWidth="1" min="100" max="100"/>
+    <col width="10" customWidth="1" min="101" max="101"/>
+    <col width="13" customWidth="1" min="102" max="102"/>
+    <col width="13" customWidth="1" min="103" max="103"/>
+    <col width="10" customWidth="1" min="104" max="104"/>
+    <col width="10" customWidth="1" min="105" max="105"/>
+    <col width="24" customWidth="1" min="106" max="106"/>
+    <col width="11" customWidth="1" min="107" max="107"/>
+    <col width="11" customWidth="1" min="108" max="108"/>
+    <col width="11" customWidth="1" min="109" max="109"/>
+    <col width="11" customWidth="1" min="110" max="110"/>
+    <col width="11" customWidth="1" min="111" max="111"/>
+    <col width="11" customWidth="1" min="112" max="112"/>
+    <col width="11" customWidth="1" min="113" max="113"/>
+    <col width="11" customWidth="1" min="114" max="114"/>
+    <col width="11" customWidth="1" min="115" max="115"/>
+    <col width="11" customWidth="1" min="116" max="116"/>
+    <col width="11" customWidth="1" min="117" max="117"/>
+    <col width="11" customWidth="1" min="118" max="118"/>
+    <col width="11" customWidth="1" min="119" max="119"/>
+    <col width="11" customWidth="1" min="120" max="120"/>
+    <col width="11" customWidth="1" min="121" max="121"/>
+    <col width="10" customWidth="1" min="122" max="122"/>
+    <col width="11" customWidth="1" min="123" max="123"/>
+    <col width="11" customWidth="1" min="124" max="124"/>
+    <col width="11" customWidth="1" min="125" max="125"/>
+    <col width="10" customWidth="1" min="126" max="126"/>
+    <col width="10" customWidth="1" min="127" max="127"/>
+    <col width="11" customWidth="1" min="128" max="128"/>
+    <col width="11" customWidth="1" min="129" max="129"/>
+    <col width="10" customWidth="1" min="130" max="130"/>
+    <col width="10" customWidth="1" min="131" max="131"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -514,22 +614,22 @@
           <t>PIB (glissement annuel)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Inflation IPC</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>Taux de chômage</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Écart de production</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>Bank Rate (implicite marchés)*</t>
         </is>
@@ -538,464 +638,3599 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>2022 Q2</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2022 Q3</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2022 Q4</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>2023 Q1</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2023 Q2</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2023 Q3</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>2023 Q4</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>2024 Q1</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2024 Q2</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>2024 Q3</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>2024 Q4</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>2025 Q1</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2025 Q2</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>2025 Q3</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>2025 Q4</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>2026 Q1</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>2026 Q2</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>2026 Q3</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>2026 Q4</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>2027 Q1</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>2027 Q2</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>2027 Q3</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>2027 Q4</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>2028 Q1</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>2028 Q4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>2029 Q1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>2022 Q2</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>2022 Q3</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>2022 Q4</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
         <is>
           <t>2023 Q1</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>2023 Q2</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>2023 Q3</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>2023 Q4</t>
+        </is>
+      </c>
+      <c r="AI2" s="2" t="inlineStr">
         <is>
           <t>2024 Q1</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>2024 Q2</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t>2024 Q3</t>
+        </is>
+      </c>
+      <c r="AL2" s="2" t="inlineStr">
+        <is>
+          <t>2024 Q4</t>
+        </is>
+      </c>
+      <c r="AM2" s="2" t="inlineStr">
         <is>
           <t>2025 Q1</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="AN2" s="2" t="inlineStr">
+        <is>
+          <t>2025 Q2</t>
+        </is>
+      </c>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>2025 Q3</t>
+        </is>
+      </c>
+      <c r="AP2" s="2" t="inlineStr">
+        <is>
+          <t>2025 Q4</t>
+        </is>
+      </c>
+      <c r="AQ2" s="2" t="inlineStr">
         <is>
           <t>2026 Q1</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="AR2" s="2" t="inlineStr">
+        <is>
+          <t>2026 Q2</t>
+        </is>
+      </c>
+      <c r="AS2" s="2" t="inlineStr">
+        <is>
+          <t>2026 Q3</t>
+        </is>
+      </c>
+      <c r="AT2" s="2" t="inlineStr">
+        <is>
+          <t>2026 Q4</t>
+        </is>
+      </c>
+      <c r="AU2" s="2" t="inlineStr">
         <is>
           <t>2027 Q1</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>2027 Q2</t>
+        </is>
+      </c>
+      <c r="AW2" s="2" t="inlineStr">
+        <is>
+          <t>2027 Q3</t>
+        </is>
+      </c>
+      <c r="AX2" s="2" t="inlineStr">
+        <is>
+          <t>2027 Q4</t>
+        </is>
+      </c>
+      <c r="AY2" s="2" t="inlineStr">
         <is>
           <t>2028 Q1</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="AZ2" s="2" t="inlineStr">
+        <is>
+          <t>2028 Q4</t>
+        </is>
+      </c>
+      <c r="BA2" s="2" t="inlineStr">
+        <is>
+          <t>2029 Q1</t>
+        </is>
+      </c>
+      <c r="BB2" s="2" t="inlineStr">
+        <is>
+          <t>2022 Q2</t>
+        </is>
+      </c>
+      <c r="BC2" s="2" t="inlineStr">
+        <is>
+          <t>2022 Q3</t>
+        </is>
+      </c>
+      <c r="BD2" s="2" t="inlineStr">
+        <is>
+          <t>2022 Q4</t>
+        </is>
+      </c>
+      <c r="BE2" s="2" t="inlineStr">
         <is>
           <t>2023 Q1</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="BF2" s="2" t="inlineStr">
+        <is>
+          <t>2023 Q2</t>
+        </is>
+      </c>
+      <c r="BG2" s="2" t="inlineStr">
+        <is>
+          <t>2023 Q3</t>
+        </is>
+      </c>
+      <c r="BH2" s="2" t="inlineStr">
+        <is>
+          <t>2023 Q4</t>
+        </is>
+      </c>
+      <c r="BI2" s="2" t="inlineStr">
         <is>
           <t>2024 Q1</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="BJ2" s="2" t="inlineStr">
+        <is>
+          <t>2024 Q2</t>
+        </is>
+      </c>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>2024 Q3</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2024 Q4</t>
+        </is>
+      </c>
+      <c r="BM2" s="2" t="inlineStr">
         <is>
           <t>2025 Q1</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="BN2" s="2" t="inlineStr">
+        <is>
+          <t>2025 Q2</t>
+        </is>
+      </c>
+      <c r="BO2" s="2" t="inlineStr">
+        <is>
+          <t>2025 Q3</t>
+        </is>
+      </c>
+      <c r="BP2" s="2" t="inlineStr">
+        <is>
+          <t>2025 Q4</t>
+        </is>
+      </c>
+      <c r="BQ2" s="2" t="inlineStr">
         <is>
           <t>2026 Q1</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="BR2" s="2" t="inlineStr">
+        <is>
+          <t>2026 Q2</t>
+        </is>
+      </c>
+      <c r="BS2" s="2" t="inlineStr">
+        <is>
+          <t>2026 Q3</t>
+        </is>
+      </c>
+      <c r="BT2" s="2" t="inlineStr">
+        <is>
+          <t>2026 Q4</t>
+        </is>
+      </c>
+      <c r="BU2" s="2" t="inlineStr">
         <is>
           <t>2027 Q1</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="BV2" s="2" t="inlineStr">
+        <is>
+          <t>2027 Q2</t>
+        </is>
+      </c>
+      <c r="BW2" s="2" t="inlineStr">
+        <is>
+          <t>2027 Q3</t>
+        </is>
+      </c>
+      <c r="BX2" s="2" t="inlineStr">
+        <is>
+          <t>2027 Q4</t>
+        </is>
+      </c>
+      <c r="BY2" s="2" t="inlineStr">
         <is>
           <t>2028 Q1</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="BZ2" s="2" t="inlineStr">
+        <is>
+          <t>2028 Q4</t>
+        </is>
+      </c>
+      <c r="CA2" s="2" t="inlineStr">
+        <is>
+          <t>2029 Q1</t>
+        </is>
+      </c>
+      <c r="CB2" s="2" t="inlineStr">
+        <is>
+          <t>2022 Q2</t>
+        </is>
+      </c>
+      <c r="CC2" s="2" t="inlineStr">
+        <is>
+          <t>2022 Q3</t>
+        </is>
+      </c>
+      <c r="CD2" s="2" t="inlineStr">
+        <is>
+          <t>2022 Q4</t>
+        </is>
+      </c>
+      <c r="CE2" s="2" t="inlineStr">
         <is>
           <t>2023 Q1</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="CF2" s="2" t="inlineStr">
+        <is>
+          <t>2023 Q2</t>
+        </is>
+      </c>
+      <c r="CG2" s="2" t="inlineStr">
+        <is>
+          <t>2023 Q3</t>
+        </is>
+      </c>
+      <c r="CH2" s="2" t="inlineStr">
+        <is>
+          <t>2023 Q4</t>
+        </is>
+      </c>
+      <c r="CI2" s="2" t="inlineStr">
         <is>
           <t>2024 Q1</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="CJ2" s="2" t="inlineStr">
+        <is>
+          <t>2024 Q2</t>
+        </is>
+      </c>
+      <c r="CK2" s="2" t="inlineStr">
+        <is>
+          <t>2024 Q3</t>
+        </is>
+      </c>
+      <c r="CL2" s="2" t="inlineStr">
+        <is>
+          <t>2024 Q4</t>
+        </is>
+      </c>
+      <c r="CM2" s="2" t="inlineStr">
         <is>
           <t>2025 Q1</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="CN2" s="2" t="inlineStr">
+        <is>
+          <t>2025 Q2</t>
+        </is>
+      </c>
+      <c r="CO2" s="2" t="inlineStr">
+        <is>
+          <t>2025 Q3</t>
+        </is>
+      </c>
+      <c r="CP2" s="2" t="inlineStr">
+        <is>
+          <t>2025 Q4</t>
+        </is>
+      </c>
+      <c r="CQ2" s="2" t="inlineStr">
         <is>
           <t>2026 Q1</t>
         </is>
       </c>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="CR2" s="2" t="inlineStr">
+        <is>
+          <t>2026 Q2</t>
+        </is>
+      </c>
+      <c r="CS2" s="2" t="inlineStr">
+        <is>
+          <t>2026 Q3</t>
+        </is>
+      </c>
+      <c r="CT2" s="2" t="inlineStr">
+        <is>
+          <t>2026 Q4</t>
+        </is>
+      </c>
+      <c r="CU2" s="2" t="inlineStr">
         <is>
           <t>2027 Q1</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="CV2" s="2" t="inlineStr">
+        <is>
+          <t>2027 Q2</t>
+        </is>
+      </c>
+      <c r="CW2" s="2" t="inlineStr">
+        <is>
+          <t>2027 Q3</t>
+        </is>
+      </c>
+      <c r="CX2" s="2" t="inlineStr">
+        <is>
+          <t>2027 Q4</t>
+        </is>
+      </c>
+      <c r="CY2" s="2" t="inlineStr">
         <is>
           <t>2028 Q1</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="CZ2" s="2" t="inlineStr">
+        <is>
+          <t>2028 Q4</t>
+        </is>
+      </c>
+      <c r="DA2" s="2" t="inlineStr">
+        <is>
+          <t>2029 Q1</t>
+        </is>
+      </c>
+      <c r="DB2" s="2" t="inlineStr">
+        <is>
+          <t>2022 Q2</t>
+        </is>
+      </c>
+      <c r="DC2" s="2" t="inlineStr">
+        <is>
+          <t>2022 Q3</t>
+        </is>
+      </c>
+      <c r="DD2" s="2" t="inlineStr">
+        <is>
+          <t>2022 Q4</t>
+        </is>
+      </c>
+      <c r="DE2" s="2" t="inlineStr">
         <is>
           <t>2023 Q1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="DF2" s="2" t="inlineStr">
+        <is>
+          <t>2023 Q2</t>
+        </is>
+      </c>
+      <c r="DG2" s="2" t="inlineStr">
+        <is>
+          <t>2023 Q3</t>
+        </is>
+      </c>
+      <c r="DH2" s="2" t="inlineStr">
+        <is>
+          <t>2023 Q4</t>
+        </is>
+      </c>
+      <c r="DI2" s="2" t="inlineStr">
         <is>
           <t>2024 Q1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
+      <c r="DJ2" s="2" t="inlineStr">
+        <is>
+          <t>2024 Q2</t>
+        </is>
+      </c>
+      <c r="DK2" s="2" t="inlineStr">
+        <is>
+          <t>2024 Q3</t>
+        </is>
+      </c>
+      <c r="DL2" s="2" t="inlineStr">
+        <is>
+          <t>2024 Q4</t>
+        </is>
+      </c>
+      <c r="DM2" s="2" t="inlineStr">
         <is>
           <t>2025 Q1</t>
         </is>
       </c>
-      <c r="AC2" s="2" t="inlineStr">
+      <c r="DN2" s="2" t="inlineStr">
+        <is>
+          <t>2025 Q2</t>
+        </is>
+      </c>
+      <c r="DO2" s="2" t="inlineStr">
+        <is>
+          <t>2025 Q3</t>
+        </is>
+      </c>
+      <c r="DP2" s="2" t="inlineStr">
+        <is>
+          <t>2025 Q4</t>
+        </is>
+      </c>
+      <c r="DQ2" s="2" t="inlineStr">
         <is>
           <t>2026 Q1</t>
         </is>
       </c>
-      <c r="AD2" s="2" t="inlineStr">
+      <c r="DR2" s="2" t="inlineStr">
+        <is>
+          <t>2026 Q2</t>
+        </is>
+      </c>
+      <c r="DS2" s="2" t="inlineStr">
+        <is>
+          <t>2026 Q3</t>
+        </is>
+      </c>
+      <c r="DT2" s="2" t="inlineStr">
+        <is>
+          <t>2026 Q4</t>
+        </is>
+      </c>
+      <c r="DU2" s="2" t="inlineStr">
         <is>
           <t>2027 Q1</t>
         </is>
       </c>
-      <c r="AE2" s="2" t="inlineStr">
+      <c r="DV2" s="2" t="inlineStr">
+        <is>
+          <t>2027 Q2</t>
+        </is>
+      </c>
+      <c r="DW2" s="2" t="inlineStr">
+        <is>
+          <t>2027 Q3</t>
+        </is>
+      </c>
+      <c r="DX2" s="2" t="inlineStr">
+        <is>
+          <t>2027 Q4</t>
+        </is>
+      </c>
+      <c r="DY2" s="2" t="inlineStr">
         <is>
           <t>2028 Q1</t>
+        </is>
+      </c>
+      <c r="DZ2" s="2" t="inlineStr">
+        <is>
+          <t>2028 Q4</t>
+        </is>
+      </c>
+      <c r="EA2" s="2" t="inlineStr">
+        <is>
+          <t>2029 Q1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2023-02</t>
+          <t>2022-05</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>-0.3 (-0.6)</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>-0.7 (-2.0)</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>0.2 (0.1)</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr"/>
+          <t>3.2 (3.2)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>0.0 (1.2)</t>
+        </is>
+      </c>
       <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>9.7 (10.1)</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>3.0 (4.0)</t>
-        </is>
-      </c>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>1.0 (1.2)</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
+          <t>0.2 (1.0)</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
       <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>0 (-0.25)</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr"/>
+      <c r="V3" s="3" t="inlineStr"/>
+      <c r="W3" s="3" t="inlineStr"/>
       <c r="X3" s="3" t="inlineStr"/>
       <c r="Y3" s="3" t="inlineStr"/>
-      <c r="Z3" s="3" t="inlineStr">
-        <is>
-          <t>3.8 (4.3)</t>
-        </is>
-      </c>
-      <c r="AA3" s="3" t="inlineStr">
-        <is>
-          <t>4.3 (5.1)</t>
-        </is>
-      </c>
+      <c r="Z3" s="3" t="inlineStr"/>
+      <c r="AA3" s="3" t="inlineStr"/>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>3.6 (4.7)</t>
-        </is>
-      </c>
-      <c r="AC3" s="3" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
+          <t>9.1 (7.0)</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr"/>
       <c r="AD3" s="3" t="inlineStr"/>
       <c r="AE3" s="3" t="inlineStr"/>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>6.6 (3.5)</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr"/>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="3" t="inlineStr">
+        <is>
+          <t>2.1 (1.9)</t>
+        </is>
+      </c>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr"/>
+      <c r="AM3" s="3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr"/>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr"/>
+      <c r="AS3" s="3" t="inlineStr"/>
+      <c r="AT3" s="3" t="inlineStr"/>
+      <c r="AU3" s="3" t="inlineStr"/>
+      <c r="AV3" s="3" t="inlineStr"/>
+      <c r="AW3" s="3" t="inlineStr"/>
+      <c r="AX3" s="3" t="inlineStr"/>
+      <c r="AY3" s="3" t="inlineStr"/>
+      <c r="AZ3" s="3" t="inlineStr"/>
+      <c r="BA3" s="3" t="inlineStr"/>
+      <c r="BB3" s="3" t="inlineStr"/>
+      <c r="BC3" s="3" t="inlineStr"/>
+      <c r="BD3" s="3" t="inlineStr"/>
+      <c r="BE3" s="3" t="inlineStr"/>
+      <c r="BF3" s="3" t="inlineStr"/>
+      <c r="BG3" s="3" t="inlineStr"/>
+      <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr"/>
+      <c r="BL3" s="3" t="inlineStr"/>
+      <c r="BM3" s="3" t="inlineStr"/>
+      <c r="BN3" s="3" t="inlineStr"/>
+      <c r="BO3" s="3" t="inlineStr"/>
+      <c r="BP3" s="3" t="inlineStr"/>
+      <c r="BQ3" s="3" t="inlineStr"/>
+      <c r="BR3" s="3" t="inlineStr"/>
+      <c r="BS3" s="3" t="inlineStr"/>
+      <c r="BT3" s="3" t="inlineStr"/>
+      <c r="BU3" s="3" t="inlineStr"/>
+      <c r="BV3" s="3" t="inlineStr"/>
+      <c r="BW3" s="3" t="inlineStr"/>
+      <c r="BX3" s="3" t="inlineStr"/>
+      <c r="BY3" s="3" t="inlineStr"/>
+      <c r="BZ3" s="3" t="inlineStr"/>
+      <c r="CA3" s="3" t="inlineStr"/>
+      <c r="CB3" s="3" t="inlineStr">
+        <is>
+          <t>0.5 (0)</t>
+        </is>
+      </c>
+      <c r="CC3" s="3" t="inlineStr"/>
+      <c r="CD3" s="3" t="inlineStr"/>
+      <c r="CE3" s="3" t="inlineStr"/>
+      <c r="CF3" s="3" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="CG3" s="3" t="inlineStr"/>
+      <c r="CH3" s="3" t="inlineStr"/>
+      <c r="CI3" s="3" t="inlineStr"/>
+      <c r="CJ3" s="3" t="inlineStr">
+        <is>
+          <t>0.25 (-0.5)</t>
+        </is>
+      </c>
+      <c r="CK3" s="3" t="inlineStr"/>
+      <c r="CL3" s="3" t="inlineStr"/>
+      <c r="CM3" s="3" t="inlineStr"/>
+      <c r="CN3" s="3" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="CO3" s="3" t="inlineStr"/>
+      <c r="CP3" s="3" t="inlineStr"/>
+      <c r="CQ3" s="3" t="inlineStr"/>
+      <c r="CR3" s="3" t="inlineStr"/>
+      <c r="CS3" s="3" t="inlineStr"/>
+      <c r="CT3" s="3" t="inlineStr"/>
+      <c r="CU3" s="3" t="inlineStr"/>
+      <c r="CV3" s="3" t="inlineStr"/>
+      <c r="CW3" s="3" t="inlineStr"/>
+      <c r="CX3" s="3" t="inlineStr"/>
+      <c r="CY3" s="3" t="inlineStr"/>
+      <c r="CZ3" s="3" t="inlineStr"/>
+      <c r="DA3" s="3" t="inlineStr"/>
+      <c r="DB3" s="3" t="inlineStr">
+        <is>
+          <t>1.0 (0.7)</t>
+        </is>
+      </c>
+      <c r="DC3" s="3" t="inlineStr"/>
+      <c r="DD3" s="3" t="inlineStr"/>
+      <c r="DE3" s="3" t="inlineStr"/>
+      <c r="DF3" s="3" t="inlineStr">
+        <is>
+          <t>2.5 (1.4)</t>
+        </is>
+      </c>
+      <c r="DG3" s="3" t="inlineStr"/>
+      <c r="DH3" s="3" t="inlineStr"/>
+      <c r="DI3" s="3" t="inlineStr"/>
+      <c r="DJ3" s="3" t="inlineStr">
+        <is>
+          <t>2.4 (1.4)</t>
+        </is>
+      </c>
+      <c r="DK3" s="3" t="inlineStr"/>
+      <c r="DL3" s="3" t="inlineStr"/>
+      <c r="DM3" s="3" t="inlineStr"/>
+      <c r="DN3" s="3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="DO3" s="3" t="inlineStr"/>
+      <c r="DP3" s="3" t="inlineStr"/>
+      <c r="DQ3" s="3" t="inlineStr"/>
+      <c r="DR3" s="3" t="inlineStr"/>
+      <c r="DS3" s="3" t="inlineStr"/>
+      <c r="DT3" s="3" t="inlineStr"/>
+      <c r="DU3" s="3" t="inlineStr"/>
+      <c r="DV3" s="3" t="inlineStr"/>
+      <c r="DW3" s="3" t="inlineStr"/>
+      <c r="DX3" s="3" t="inlineStr"/>
+      <c r="DY3" s="3" t="inlineStr"/>
+      <c r="DZ3" s="3" t="inlineStr"/>
+      <c r="EA3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr"/>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.3 (2.9)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr"/>
       <c r="E4" s="3" t="inlineStr"/>
       <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>-2.1 (-0.8)</t>
+        </is>
+      </c>
       <c r="H4" s="3" t="inlineStr"/>
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>0.0 (0.4)</t>
+        </is>
+      </c>
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="3" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>4.4 (4.4)</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>4.7 (4.8)</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>4.9 (5.0)</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
-      </c>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>-0.25 (-0.25)</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>-0.5 (-1)</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
+      <c r="U4" s="3" t="inlineStr"/>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
       <c r="Z4" s="3" t="inlineStr"/>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AA4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr"/>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+          <t>9.9 (9.5)</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
       <c r="AE4" s="3" t="inlineStr"/>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>9.5 (5.9)</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr">
+        <is>
+          <t>2.0 (1.8)</t>
+        </is>
+      </c>
+      <c r="AL4" s="3" t="inlineStr"/>
+      <c r="AM4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr"/>
+      <c r="AS4" s="3" t="inlineStr"/>
+      <c r="AT4" s="3" t="inlineStr"/>
+      <c r="AU4" s="3" t="inlineStr"/>
+      <c r="AV4" s="3" t="inlineStr"/>
+      <c r="AW4" s="3" t="inlineStr"/>
+      <c r="AX4" s="3" t="inlineStr"/>
+      <c r="AY4" s="3" t="inlineStr"/>
+      <c r="AZ4" s="3" t="inlineStr"/>
+      <c r="BA4" s="3" t="inlineStr"/>
+      <c r="BB4" s="3" t="inlineStr"/>
+      <c r="BC4" s="3" t="inlineStr"/>
+      <c r="BD4" s="3" t="inlineStr"/>
+      <c r="BE4" s="3" t="inlineStr"/>
+      <c r="BF4" s="3" t="inlineStr"/>
+      <c r="BG4" s="3" t="inlineStr"/>
+      <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr"/>
+      <c r="BL4" s="3" t="inlineStr"/>
+      <c r="BM4" s="3" t="inlineStr"/>
+      <c r="BN4" s="3" t="inlineStr"/>
+      <c r="BO4" s="3" t="inlineStr"/>
+      <c r="BP4" s="3" t="inlineStr"/>
+      <c r="BQ4" s="3" t="inlineStr"/>
+      <c r="BR4" s="3" t="inlineStr"/>
+      <c r="BS4" s="3" t="inlineStr"/>
+      <c r="BT4" s="3" t="inlineStr"/>
+      <c r="BU4" s="3" t="inlineStr"/>
+      <c r="BV4" s="3" t="inlineStr"/>
+      <c r="BW4" s="3" t="inlineStr"/>
+      <c r="BX4" s="3" t="inlineStr"/>
+      <c r="BY4" s="3" t="inlineStr"/>
+      <c r="BZ4" s="3" t="inlineStr"/>
+      <c r="CA4" s="3" t="inlineStr"/>
+      <c r="CB4" s="3" t="inlineStr"/>
+      <c r="CC4" s="3" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="CD4" s="3" t="inlineStr"/>
+      <c r="CE4" s="3" t="inlineStr"/>
+      <c r="CF4" s="3" t="inlineStr"/>
+      <c r="CG4" s="3" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="CH4" s="3" t="inlineStr"/>
+      <c r="CI4" s="3" t="inlineStr"/>
+      <c r="CJ4" s="3" t="inlineStr"/>
+      <c r="CK4" s="3" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="CL4" s="3" t="inlineStr"/>
+      <c r="CM4" s="3" t="inlineStr"/>
+      <c r="CN4" s="3" t="inlineStr"/>
+      <c r="CO4" s="3" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="CP4" s="3" t="inlineStr"/>
+      <c r="CQ4" s="3" t="inlineStr"/>
+      <c r="CR4" s="3" t="inlineStr"/>
+      <c r="CS4" s="3" t="inlineStr"/>
+      <c r="CT4" s="3" t="inlineStr"/>
+      <c r="CU4" s="3" t="inlineStr"/>
+      <c r="CV4" s="3" t="inlineStr"/>
+      <c r="CW4" s="3" t="inlineStr"/>
+      <c r="CX4" s="3" t="inlineStr"/>
+      <c r="CY4" s="3" t="inlineStr"/>
+      <c r="CZ4" s="3" t="inlineStr"/>
+      <c r="DA4" s="3" t="inlineStr"/>
+      <c r="DB4" s="3" t="inlineStr"/>
+      <c r="DC4" s="3" t="inlineStr">
+        <is>
+          <t>1.6 (1.5)</t>
+        </is>
+      </c>
+      <c r="DD4" s="3" t="inlineStr"/>
+      <c r="DE4" s="3" t="inlineStr"/>
+      <c r="DF4" s="3" t="inlineStr"/>
+      <c r="DG4" s="3" t="inlineStr">
+        <is>
+          <t>3.0 (2.6)</t>
+        </is>
+      </c>
+      <c r="DH4" s="3" t="inlineStr"/>
+      <c r="DI4" s="3" t="inlineStr"/>
+      <c r="DJ4" s="3" t="inlineStr"/>
+      <c r="DK4" s="3" t="inlineStr">
+        <is>
+          <t>2.5 (2.3)</t>
+        </is>
+      </c>
+      <c r="DL4" s="3" t="inlineStr"/>
+      <c r="DM4" s="3" t="inlineStr"/>
+      <c r="DN4" s="3" t="inlineStr"/>
+      <c r="DO4" s="3" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="DP4" s="3" t="inlineStr"/>
+      <c r="DQ4" s="3" t="inlineStr"/>
+      <c r="DR4" s="3" t="inlineStr"/>
+      <c r="DS4" s="3" t="inlineStr"/>
+      <c r="DT4" s="3" t="inlineStr"/>
+      <c r="DU4" s="3" t="inlineStr"/>
+      <c r="DV4" s="3" t="inlineStr"/>
+      <c r="DW4" s="3" t="inlineStr"/>
+      <c r="DX4" s="3" t="inlineStr"/>
+      <c r="DY4" s="3" t="inlineStr"/>
+      <c r="DZ4" s="3" t="inlineStr"/>
+      <c r="EA4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2022-11</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>0.4 (1.4)</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>1.5 (1.6)</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>1.3 (1.1)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr"/>
+          <t>0.2 (0.1)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>-1.9 (-1.2)</t>
+        </is>
+      </c>
       <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>2.8 (2.4)</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>3 (2.6)</t>
-        </is>
-      </c>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>2.3 (2.1)</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
+          <t>-0.1 (0.1)</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>4.5 (4.1)</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>4.5 (4.2)</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t>4.8 (4.3)</t>
-        </is>
-      </c>
-      <c r="S5" s="3" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t>-0.25 (0)</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t>-0.5 (-0.25)</t>
-        </is>
-      </c>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>-0.75 (-0.5)</t>
-        </is>
-      </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="inlineStr"/>
+      <c r="Y5" s="3" t="inlineStr"/>
       <c r="Z5" s="3" t="inlineStr"/>
       <c r="AA5" s="3" t="inlineStr"/>
-      <c r="AB5" s="3" t="inlineStr">
-        <is>
-          <t>4.6 (4.4)</t>
-        </is>
-      </c>
-      <c r="AC5" s="3" t="inlineStr">
-        <is>
-          <t>4.2 (3.7)</t>
-        </is>
-      </c>
+      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AC5" s="3" t="inlineStr"/>
       <c r="AD5" s="3" t="inlineStr">
         <is>
-          <t>4.1 (3.6)</t>
-        </is>
-      </c>
-      <c r="AE5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>10.9 (13.1)</t>
+        </is>
+      </c>
+      <c r="AE5" s="3" t="inlineStr"/>
+      <c r="AF5" s="3" t="inlineStr"/>
+      <c r="AG5" s="3" t="inlineStr"/>
+      <c r="AH5" s="3" t="inlineStr">
+        <is>
+          <t>5.2 (5.5)</t>
+        </is>
+      </c>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>1.4 (1.4)</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr"/>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr"/>
+      <c r="AS5" s="3" t="inlineStr"/>
+      <c r="AT5" s="3" t="inlineStr"/>
+      <c r="AU5" s="3" t="inlineStr"/>
+      <c r="AV5" s="3" t="inlineStr"/>
+      <c r="AW5" s="3" t="inlineStr"/>
+      <c r="AX5" s="3" t="inlineStr"/>
+      <c r="AY5" s="3" t="inlineStr"/>
+      <c r="AZ5" s="3" t="inlineStr"/>
+      <c r="BA5" s="3" t="inlineStr"/>
+      <c r="BB5" s="3" t="inlineStr"/>
+      <c r="BC5" s="3" t="inlineStr"/>
+      <c r="BD5" s="3" t="inlineStr"/>
+      <c r="BE5" s="3" t="inlineStr"/>
+      <c r="BF5" s="3" t="inlineStr"/>
+      <c r="BG5" s="3" t="inlineStr"/>
+      <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr"/>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr"/>
+      <c r="BL5" s="3" t="inlineStr"/>
+      <c r="BM5" s="3" t="inlineStr"/>
+      <c r="BN5" s="3" t="inlineStr"/>
+      <c r="BO5" s="3" t="inlineStr"/>
+      <c r="BP5" s="3" t="inlineStr"/>
+      <c r="BQ5" s="3" t="inlineStr"/>
+      <c r="BR5" s="3" t="inlineStr"/>
+      <c r="BS5" s="3" t="inlineStr"/>
+      <c r="BT5" s="3" t="inlineStr"/>
+      <c r="BU5" s="3" t="inlineStr"/>
+      <c r="BV5" s="3" t="inlineStr"/>
+      <c r="BW5" s="3" t="inlineStr"/>
+      <c r="BX5" s="3" t="inlineStr"/>
+      <c r="BY5" s="3" t="inlineStr"/>
+      <c r="BZ5" s="3" t="inlineStr"/>
+      <c r="CA5" s="3" t="inlineStr"/>
+      <c r="CB5" s="3" t="inlineStr"/>
+      <c r="CC5" s="3" t="inlineStr"/>
+      <c r="CD5" s="3" t="inlineStr">
+        <is>
+          <t>0.75 (-0.25)</t>
+        </is>
+      </c>
+      <c r="CE5" s="3" t="inlineStr"/>
+      <c r="CF5" s="3" t="inlineStr"/>
+      <c r="CG5" s="3" t="inlineStr"/>
+      <c r="CH5" s="3" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="CI5" s="3" t="inlineStr"/>
+      <c r="CJ5" s="3" t="inlineStr"/>
+      <c r="CK5" s="3" t="inlineStr"/>
+      <c r="CL5" s="3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="CM5" s="3" t="inlineStr"/>
+      <c r="CN5" s="3" t="inlineStr"/>
+      <c r="CO5" s="3" t="inlineStr"/>
+      <c r="CP5" s="3" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="CQ5" s="3" t="inlineStr"/>
+      <c r="CR5" s="3" t="inlineStr"/>
+      <c r="CS5" s="3" t="inlineStr"/>
+      <c r="CT5" s="3" t="inlineStr"/>
+      <c r="CU5" s="3" t="inlineStr"/>
+      <c r="CV5" s="3" t="inlineStr"/>
+      <c r="CW5" s="3" t="inlineStr"/>
+      <c r="CX5" s="3" t="inlineStr"/>
+      <c r="CY5" s="3" t="inlineStr"/>
+      <c r="CZ5" s="3" t="inlineStr"/>
+      <c r="DA5" s="3" t="inlineStr"/>
+      <c r="DB5" s="3" t="inlineStr"/>
+      <c r="DC5" s="3" t="inlineStr"/>
+      <c r="DD5" s="3" t="inlineStr">
+        <is>
+          <t>3.0 (2.4)</t>
+        </is>
+      </c>
+      <c r="DE5" s="3" t="inlineStr"/>
+      <c r="DF5" s="3" t="inlineStr"/>
+      <c r="DG5" s="3" t="inlineStr"/>
+      <c r="DH5" s="3" t="inlineStr">
+        <is>
+          <t>5.2 (2.9)</t>
+        </is>
+      </c>
+      <c r="DI5" s="3" t="inlineStr"/>
+      <c r="DJ5" s="3" t="inlineStr"/>
+      <c r="DK5" s="3" t="inlineStr"/>
+      <c r="DL5" s="3" t="inlineStr">
+        <is>
+          <t>4.7 (2.4)</t>
+        </is>
+      </c>
+      <c r="DM5" s="3" t="inlineStr"/>
+      <c r="DN5" s="3" t="inlineStr"/>
+      <c r="DO5" s="3" t="inlineStr"/>
+      <c r="DP5" s="3" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="DQ5" s="3" t="inlineStr"/>
+      <c r="DR5" s="3" t="inlineStr"/>
+      <c r="DS5" s="3" t="inlineStr"/>
+      <c r="DT5" s="3" t="inlineStr"/>
+      <c r="DU5" s="3" t="inlineStr"/>
+      <c r="DV5" s="3" t="inlineStr"/>
+      <c r="DW5" s="3" t="inlineStr"/>
+      <c r="DX5" s="3" t="inlineStr"/>
+      <c r="DY5" s="3" t="inlineStr"/>
+      <c r="DZ5" s="3" t="inlineStr"/>
+      <c r="EA5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>-0.3 (-0.6)</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>-0.7 (-2.0)</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>0.2 (0.1)</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr"/>
+      <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" s="3" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr"/>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr"/>
+      <c r="AA6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AC6" s="3" t="inlineStr"/>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>9.7 (10.1)</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr"/>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>3.0 (4.0)</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>1.0 (1.2)</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="AR6" s="3" t="inlineStr"/>
+      <c r="AS6" s="3" t="inlineStr"/>
+      <c r="AT6" s="3" t="inlineStr"/>
+      <c r="AU6" s="3" t="inlineStr"/>
+      <c r="AV6" s="3" t="inlineStr"/>
+      <c r="AW6" s="3" t="inlineStr"/>
+      <c r="AX6" s="3" t="inlineStr"/>
+      <c r="AY6" s="3" t="inlineStr"/>
+      <c r="AZ6" s="3" t="inlineStr"/>
+      <c r="BA6" s="3" t="inlineStr"/>
+      <c r="BB6" s="3" t="inlineStr"/>
+      <c r="BC6" s="3" t="inlineStr"/>
+      <c r="BD6" s="3" t="inlineStr"/>
+      <c r="BE6" s="3" t="inlineStr"/>
+      <c r="BF6" s="3" t="inlineStr"/>
+      <c r="BG6" s="3" t="inlineStr"/>
+      <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr"/>
+      <c r="BL6" s="3" t="inlineStr"/>
+      <c r="BM6" s="3" t="inlineStr"/>
+      <c r="BN6" s="3" t="inlineStr"/>
+      <c r="BO6" s="3" t="inlineStr"/>
+      <c r="BP6" s="3" t="inlineStr"/>
+      <c r="BQ6" s="3" t="inlineStr"/>
+      <c r="BR6" s="3" t="inlineStr"/>
+      <c r="BS6" s="3" t="inlineStr"/>
+      <c r="BT6" s="3" t="inlineStr"/>
+      <c r="BU6" s="3" t="inlineStr"/>
+      <c r="BV6" s="3" t="inlineStr"/>
+      <c r="BW6" s="3" t="inlineStr"/>
+      <c r="BX6" s="3" t="inlineStr"/>
+      <c r="BY6" s="3" t="inlineStr"/>
+      <c r="BZ6" s="3" t="inlineStr"/>
+      <c r="CA6" s="3" t="inlineStr"/>
+      <c r="CB6" s="3" t="inlineStr"/>
+      <c r="CC6" s="3" t="inlineStr"/>
+      <c r="CD6" s="3" t="inlineStr"/>
+      <c r="CE6" s="3" t="inlineStr">
+        <is>
+          <t>0 (-0.25)</t>
+        </is>
+      </c>
+      <c r="CF6" s="3" t="inlineStr"/>
+      <c r="CG6" s="3" t="inlineStr"/>
+      <c r="CH6" s="3" t="inlineStr"/>
+      <c r="CI6" s="3" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="CJ6" s="3" t="inlineStr"/>
+      <c r="CK6" s="3" t="inlineStr"/>
+      <c r="CL6" s="3" t="inlineStr"/>
+      <c r="CM6" s="3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="CN6" s="3" t="inlineStr"/>
+      <c r="CO6" s="3" t="inlineStr"/>
+      <c r="CP6" s="3" t="inlineStr"/>
+      <c r="CQ6" s="3" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="CR6" s="3" t="inlineStr"/>
+      <c r="CS6" s="3" t="inlineStr"/>
+      <c r="CT6" s="3" t="inlineStr"/>
+      <c r="CU6" s="3" t="inlineStr"/>
+      <c r="CV6" s="3" t="inlineStr"/>
+      <c r="CW6" s="3" t="inlineStr"/>
+      <c r="CX6" s="3" t="inlineStr"/>
+      <c r="CY6" s="3" t="inlineStr"/>
+      <c r="CZ6" s="3" t="inlineStr"/>
+      <c r="DA6" s="3" t="inlineStr"/>
+      <c r="DB6" s="3" t="inlineStr"/>
+      <c r="DC6" s="3" t="inlineStr"/>
+      <c r="DD6" s="3" t="inlineStr"/>
+      <c r="DE6" s="3" t="inlineStr">
+        <is>
+          <t>3.8 (4.3)</t>
+        </is>
+      </c>
+      <c r="DF6" s="3" t="inlineStr"/>
+      <c r="DG6" s="3" t="inlineStr"/>
+      <c r="DH6" s="3" t="inlineStr"/>
+      <c r="DI6" s="3" t="inlineStr">
+        <is>
+          <t>4.3 (5.1)</t>
+        </is>
+      </c>
+      <c r="DJ6" s="3" t="inlineStr"/>
+      <c r="DK6" s="3" t="inlineStr"/>
+      <c r="DL6" s="3" t="inlineStr"/>
+      <c r="DM6" s="3" t="inlineStr">
+        <is>
+          <t>3.6 (4.7)</t>
+        </is>
+      </c>
+      <c r="DN6" s="3" t="inlineStr"/>
+      <c r="DO6" s="3" t="inlineStr"/>
+      <c r="DP6" s="3" t="inlineStr"/>
+      <c r="DQ6" s="3" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="DR6" s="3" t="inlineStr"/>
+      <c r="DS6" s="3" t="inlineStr"/>
+      <c r="DT6" s="3" t="inlineStr"/>
+      <c r="DU6" s="3" t="inlineStr"/>
+      <c r="DV6" s="3" t="inlineStr"/>
+      <c r="DW6" s="3" t="inlineStr"/>
+      <c r="DX6" s="3" t="inlineStr"/>
+      <c r="DY6" s="3" t="inlineStr"/>
+      <c r="DZ6" s="3" t="inlineStr"/>
+      <c r="EA6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>0 (-0.7)</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>0.9 (-0.3)</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>0.7 (0.2)</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr"/>
+      <c r="V7" s="3" t="inlineStr"/>
+      <c r="W7" s="3" t="inlineStr"/>
+      <c r="X7" s="3" t="inlineStr"/>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr"/>
+      <c r="AA7" s="3" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AC7" s="3" t="inlineStr"/>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr"/>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>8.2 (8.5)</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr"/>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr">
+        <is>
+          <t>3.4 (1.0)</t>
+        </is>
+      </c>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr"/>
+      <c r="AM7" s="3" t="inlineStr"/>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>1.1 (0.8)</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr"/>
+      <c r="AT7" s="3" t="inlineStr"/>
+      <c r="AU7" s="3" t="inlineStr"/>
+      <c r="AV7" s="3" t="inlineStr"/>
+      <c r="AW7" s="3" t="inlineStr"/>
+      <c r="AX7" s="3" t="inlineStr"/>
+      <c r="AY7" s="3" t="inlineStr"/>
+      <c r="AZ7" s="3" t="inlineStr"/>
+      <c r="BA7" s="3" t="inlineStr"/>
+      <c r="BB7" s="3" t="inlineStr"/>
+      <c r="BC7" s="3" t="inlineStr"/>
+      <c r="BD7" s="3" t="inlineStr"/>
+      <c r="BE7" s="3" t="inlineStr"/>
+      <c r="BF7" s="3" t="inlineStr"/>
+      <c r="BG7" s="3" t="inlineStr"/>
+      <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr"/>
+      <c r="BL7" s="3" t="inlineStr"/>
+      <c r="BM7" s="3" t="inlineStr"/>
+      <c r="BN7" s="3" t="inlineStr"/>
+      <c r="BO7" s="3" t="inlineStr"/>
+      <c r="BP7" s="3" t="inlineStr"/>
+      <c r="BQ7" s="3" t="inlineStr"/>
+      <c r="BR7" s="3" t="inlineStr"/>
+      <c r="BS7" s="3" t="inlineStr"/>
+      <c r="BT7" s="3" t="inlineStr"/>
+      <c r="BU7" s="3" t="inlineStr"/>
+      <c r="BV7" s="3" t="inlineStr"/>
+      <c r="BW7" s="3" t="inlineStr"/>
+      <c r="BX7" s="3" t="inlineStr"/>
+      <c r="BY7" s="3" t="inlineStr"/>
+      <c r="BZ7" s="3" t="inlineStr"/>
+      <c r="CA7" s="3" t="inlineStr"/>
+      <c r="CB7" s="3" t="inlineStr"/>
+      <c r="CC7" s="3" t="inlineStr"/>
+      <c r="CD7" s="3" t="inlineStr"/>
+      <c r="CE7" s="3" t="inlineStr"/>
+      <c r="CF7" s="3" t="inlineStr">
+        <is>
+          <t>0.25 (-0.75)</t>
+        </is>
+      </c>
+      <c r="CG7" s="3" t="inlineStr"/>
+      <c r="CH7" s="3" t="inlineStr"/>
+      <c r="CI7" s="3" t="inlineStr"/>
+      <c r="CJ7" s="3" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="CK7" s="3" t="inlineStr"/>
+      <c r="CL7" s="3" t="inlineStr"/>
+      <c r="CM7" s="3" t="inlineStr"/>
+      <c r="CN7" s="3" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="CO7" s="3" t="inlineStr"/>
+      <c r="CP7" s="3" t="inlineStr"/>
+      <c r="CQ7" s="3" t="inlineStr"/>
+      <c r="CR7" s="3" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="CS7" s="3" t="inlineStr"/>
+      <c r="CT7" s="3" t="inlineStr"/>
+      <c r="CU7" s="3" t="inlineStr"/>
+      <c r="CV7" s="3" t="inlineStr"/>
+      <c r="CW7" s="3" t="inlineStr"/>
+      <c r="CX7" s="3" t="inlineStr"/>
+      <c r="CY7" s="3" t="inlineStr"/>
+      <c r="CZ7" s="3" t="inlineStr"/>
+      <c r="DA7" s="3" t="inlineStr"/>
+      <c r="DB7" s="3" t="inlineStr"/>
+      <c r="DC7" s="3" t="inlineStr"/>
+      <c r="DD7" s="3" t="inlineStr"/>
+      <c r="DE7" s="3" t="inlineStr"/>
+      <c r="DF7" s="3" t="inlineStr">
+        <is>
+          <t>4.4 (4.3)</t>
+        </is>
+      </c>
+      <c r="DG7" s="3" t="inlineStr"/>
+      <c r="DH7" s="3" t="inlineStr"/>
+      <c r="DI7" s="3" t="inlineStr"/>
+      <c r="DJ7" s="3" t="inlineStr">
+        <is>
+          <t>4.4 (4.1)</t>
+        </is>
+      </c>
+      <c r="DK7" s="3" t="inlineStr"/>
+      <c r="DL7" s="3" t="inlineStr"/>
+      <c r="DM7" s="3" t="inlineStr"/>
+      <c r="DN7" s="3" t="inlineStr">
+        <is>
+          <t>3.8 (3.5)</t>
+        </is>
+      </c>
+      <c r="DO7" s="3" t="inlineStr"/>
+      <c r="DP7" s="3" t="inlineStr"/>
+      <c r="DQ7" s="3" t="inlineStr"/>
+      <c r="DR7" s="3" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="DS7" s="3" t="inlineStr"/>
+      <c r="DT7" s="3" t="inlineStr"/>
+      <c r="DU7" s="3" t="inlineStr"/>
+      <c r="DV7" s="3" t="inlineStr"/>
+      <c r="DW7" s="3" t="inlineStr"/>
+      <c r="DX7" s="3" t="inlineStr"/>
+      <c r="DY7" s="3" t="inlineStr"/>
+      <c r="DZ7" s="3" t="inlineStr"/>
+      <c r="EA7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>0.8 (0.6)</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>0.3 (0.6)</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="inlineStr"/>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>0.3 (0.8)</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr"/>
+      <c r="V8" s="3" t="inlineStr"/>
+      <c r="W8" s="3" t="inlineStr"/>
+      <c r="X8" s="3" t="inlineStr"/>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr"/>
+      <c r="AA8" s="3" t="inlineStr"/>
+      <c r="AB8" s="3" t="inlineStr"/>
+      <c r="AC8" s="3" t="inlineStr"/>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr"/>
+      <c r="AF8" s="3" t="inlineStr"/>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>6.9 (7.0)</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr">
+        <is>
+          <t>2.8 (2.9)</t>
+        </is>
+      </c>
+      <c r="AL8" s="3" t="inlineStr"/>
+      <c r="AM8" s="3" t="inlineStr"/>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>1.7 (1.0)</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr"/>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr"/>
+      <c r="AU8" s="3" t="inlineStr"/>
+      <c r="AV8" s="3" t="inlineStr"/>
+      <c r="AW8" s="3" t="inlineStr"/>
+      <c r="AX8" s="3" t="inlineStr"/>
+      <c r="AY8" s="3" t="inlineStr"/>
+      <c r="AZ8" s="3" t="inlineStr"/>
+      <c r="BA8" s="3" t="inlineStr"/>
+      <c r="BB8" s="3" t="inlineStr"/>
+      <c r="BC8" s="3" t="inlineStr"/>
+      <c r="BD8" s="3" t="inlineStr"/>
+      <c r="BE8" s="3" t="inlineStr"/>
+      <c r="BF8" s="3" t="inlineStr"/>
+      <c r="BG8" s="3" t="inlineStr"/>
+      <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr"/>
+      <c r="BJ8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr"/>
+      <c r="BL8" s="3" t="inlineStr"/>
+      <c r="BM8" s="3" t="inlineStr"/>
+      <c r="BN8" s="3" t="inlineStr"/>
+      <c r="BO8" s="3" t="inlineStr"/>
+      <c r="BP8" s="3" t="inlineStr"/>
+      <c r="BQ8" s="3" t="inlineStr"/>
+      <c r="BR8" s="3" t="inlineStr"/>
+      <c r="BS8" s="3" t="inlineStr"/>
+      <c r="BT8" s="3" t="inlineStr"/>
+      <c r="BU8" s="3" t="inlineStr"/>
+      <c r="BV8" s="3" t="inlineStr"/>
+      <c r="BW8" s="3" t="inlineStr"/>
+      <c r="BX8" s="3" t="inlineStr"/>
+      <c r="BY8" s="3" t="inlineStr"/>
+      <c r="BZ8" s="3" t="inlineStr"/>
+      <c r="CA8" s="3" t="inlineStr"/>
+      <c r="CB8" s="3" t="inlineStr"/>
+      <c r="CC8" s="3" t="inlineStr"/>
+      <c r="CD8" s="3" t="inlineStr"/>
+      <c r="CE8" s="3" t="inlineStr"/>
+      <c r="CF8" s="3" t="inlineStr"/>
+      <c r="CG8" s="3" t="inlineStr">
+        <is>
+          <t>0.5 (0)</t>
+        </is>
+      </c>
+      <c r="CH8" s="3" t="inlineStr"/>
+      <c r="CI8" s="3" t="inlineStr"/>
+      <c r="CJ8" s="3" t="inlineStr"/>
+      <c r="CK8" s="3" t="inlineStr">
+        <is>
+          <t>-0.5 (-0.75)</t>
+        </is>
+      </c>
+      <c r="CL8" s="3" t="inlineStr"/>
+      <c r="CM8" s="3" t="inlineStr"/>
+      <c r="CN8" s="3" t="inlineStr"/>
+      <c r="CO8" s="3" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="CP8" s="3" t="inlineStr"/>
+      <c r="CQ8" s="3" t="inlineStr"/>
+      <c r="CR8" s="3" t="inlineStr"/>
+      <c r="CS8" s="3" t="inlineStr">
+        <is>
+          <t>0.25 (-1)</t>
+        </is>
+      </c>
+      <c r="CT8" s="3" t="inlineStr"/>
+      <c r="CU8" s="3" t="inlineStr"/>
+      <c r="CV8" s="3" t="inlineStr"/>
+      <c r="CW8" s="3" t="inlineStr"/>
+      <c r="CX8" s="3" t="inlineStr"/>
+      <c r="CY8" s="3" t="inlineStr"/>
+      <c r="CZ8" s="3" t="inlineStr"/>
+      <c r="DA8" s="3" t="inlineStr"/>
+      <c r="DB8" s="3" t="inlineStr"/>
+      <c r="DC8" s="3" t="inlineStr"/>
+      <c r="DD8" s="3" t="inlineStr"/>
+      <c r="DE8" s="3" t="inlineStr"/>
+      <c r="DF8" s="3" t="inlineStr"/>
+      <c r="DG8" s="3" t="inlineStr">
+        <is>
+          <t>5.3 (4.7)</t>
+        </is>
+      </c>
+      <c r="DH8" s="3" t="inlineStr"/>
+      <c r="DI8" s="3" t="inlineStr"/>
+      <c r="DJ8" s="3" t="inlineStr"/>
+      <c r="DK8" s="3" t="inlineStr">
+        <is>
+          <t>6.0 (4.2)</t>
+        </is>
+      </c>
+      <c r="DL8" s="3" t="inlineStr"/>
+      <c r="DM8" s="3" t="inlineStr"/>
+      <c r="DN8" s="3" t="inlineStr"/>
+      <c r="DO8" s="3" t="inlineStr">
+        <is>
+          <t>5.2 (3.7)</t>
+        </is>
+      </c>
+      <c r="DP8" s="3" t="inlineStr"/>
+      <c r="DQ8" s="3" t="inlineStr"/>
+      <c r="DR8" s="3" t="inlineStr"/>
+      <c r="DS8" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="DT8" s="3" t="inlineStr"/>
+      <c r="DU8" s="3" t="inlineStr"/>
+      <c r="DV8" s="3" t="inlineStr"/>
+      <c r="DW8" s="3" t="inlineStr"/>
+      <c r="DX8" s="3" t="inlineStr"/>
+      <c r="DY8" s="3" t="inlineStr"/>
+      <c r="DZ8" s="3" t="inlineStr"/>
+      <c r="EA8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>0.6 (0.9)</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>0 (0.1)</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>0.4 (0.5)</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr"/>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="inlineStr"/>
+      <c r="V9" s="3" t="inlineStr"/>
+      <c r="W9" s="3" t="inlineStr"/>
+      <c r="X9" s="3" t="inlineStr"/>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr"/>
+      <c r="AA9" s="3" t="inlineStr"/>
+      <c r="AB9" s="3" t="inlineStr"/>
+      <c r="AC9" s="3" t="inlineStr"/>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr"/>
+      <c r="AF9" s="3" t="inlineStr"/>
+      <c r="AG9" s="3" t="inlineStr"/>
+      <c r="AH9" s="3" t="inlineStr">
+        <is>
+          <t>4.6 (4.9)</t>
+        </is>
+      </c>
+      <c r="AI9" s="3" t="inlineStr"/>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>3.1 (2.5)</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr"/>
+      <c r="AN9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>1.9 (1.6)</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr"/>
+      <c r="AS9" s="3" t="inlineStr"/>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr"/>
+      <c r="AV9" s="3" t="inlineStr"/>
+      <c r="AW9" s="3" t="inlineStr"/>
+      <c r="AX9" s="3" t="inlineStr"/>
+      <c r="AY9" s="3" t="inlineStr"/>
+      <c r="AZ9" s="3" t="inlineStr"/>
+      <c r="BA9" s="3" t="inlineStr"/>
+      <c r="BB9" s="3" t="inlineStr"/>
+      <c r="BC9" s="3" t="inlineStr"/>
+      <c r="BD9" s="3" t="inlineStr"/>
+      <c r="BE9" s="3" t="inlineStr"/>
+      <c r="BF9" s="3" t="inlineStr"/>
+      <c r="BG9" s="3" t="inlineStr"/>
+      <c r="BH9" s="3" t="inlineStr">
+        <is>
+          <t>4.3 (4.1)</t>
+        </is>
+      </c>
+      <c r="BI9" s="3" t="inlineStr"/>
+      <c r="BJ9" s="3" t="inlineStr"/>
+      <c r="BK9" s="3" t="inlineStr"/>
+      <c r="BL9" s="3" t="inlineStr">
+        <is>
+          <t>4.7 (4.5)</t>
+        </is>
+      </c>
+      <c r="BM9" s="3" t="inlineStr"/>
+      <c r="BN9" s="3" t="inlineStr"/>
+      <c r="BO9" s="3" t="inlineStr"/>
+      <c r="BP9" s="3" t="inlineStr">
+        <is>
+          <t>5 (4.8)</t>
+        </is>
+      </c>
+      <c r="BQ9" s="3" t="inlineStr"/>
+      <c r="BR9" s="3" t="inlineStr"/>
+      <c r="BS9" s="3" t="inlineStr"/>
+      <c r="BT9" s="3" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="BU9" s="3" t="inlineStr"/>
+      <c r="BV9" s="3" t="inlineStr"/>
+      <c r="BW9" s="3" t="inlineStr"/>
+      <c r="BX9" s="3" t="inlineStr"/>
+      <c r="BY9" s="3" t="inlineStr"/>
+      <c r="BZ9" s="3" t="inlineStr"/>
+      <c r="CA9" s="3" t="inlineStr"/>
+      <c r="CB9" s="3" t="inlineStr"/>
+      <c r="CC9" s="3" t="inlineStr"/>
+      <c r="CD9" s="3" t="inlineStr"/>
+      <c r="CE9" s="3" t="inlineStr"/>
+      <c r="CF9" s="3" t="inlineStr"/>
+      <c r="CG9" s="3" t="inlineStr"/>
+      <c r="CH9" s="3" t="inlineStr">
+        <is>
+          <t>0 (0.25)</t>
+        </is>
+      </c>
+      <c r="CI9" s="3" t="inlineStr"/>
+      <c r="CJ9" s="3" t="inlineStr"/>
+      <c r="CK9" s="3" t="inlineStr"/>
+      <c r="CL9" s="3" t="inlineStr">
+        <is>
+          <t>-0.75 (-0.75)</t>
+        </is>
+      </c>
+      <c r="CM9" s="3" t="inlineStr"/>
+      <c r="CN9" s="3" t="inlineStr"/>
+      <c r="CO9" s="3" t="inlineStr"/>
+      <c r="CP9" s="3" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="CQ9" s="3" t="inlineStr"/>
+      <c r="CR9" s="3" t="inlineStr"/>
+      <c r="CS9" s="3" t="inlineStr"/>
+      <c r="CT9" s="3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="CU9" s="3" t="inlineStr"/>
+      <c r="CV9" s="3" t="inlineStr"/>
+      <c r="CW9" s="3" t="inlineStr"/>
+      <c r="CX9" s="3" t="inlineStr"/>
+      <c r="CY9" s="3" t="inlineStr"/>
+      <c r="CZ9" s="3" t="inlineStr"/>
+      <c r="DA9" s="3" t="inlineStr"/>
+      <c r="DB9" s="3" t="inlineStr"/>
+      <c r="DC9" s="3" t="inlineStr"/>
+      <c r="DD9" s="3" t="inlineStr"/>
+      <c r="DE9" s="3" t="inlineStr"/>
+      <c r="DF9" s="3" t="inlineStr"/>
+      <c r="DG9" s="3" t="inlineStr"/>
+      <c r="DH9" s="3" t="inlineStr">
+        <is>
+          <t>5.3 (5.8)</t>
+        </is>
+      </c>
+      <c r="DI9" s="3" t="inlineStr"/>
+      <c r="DJ9" s="3" t="inlineStr"/>
+      <c r="DK9" s="3" t="inlineStr"/>
+      <c r="DL9" s="3" t="inlineStr">
+        <is>
+          <t>5.1 (5.9)</t>
+        </is>
+      </c>
+      <c r="DM9" s="3" t="inlineStr"/>
+      <c r="DN9" s="3" t="inlineStr"/>
+      <c r="DO9" s="3" t="inlineStr"/>
+      <c r="DP9" s="3" t="inlineStr">
+        <is>
+          <t>4.5 (5)</t>
+        </is>
+      </c>
+      <c r="DQ9" s="3" t="inlineStr"/>
+      <c r="DR9" s="3" t="inlineStr"/>
+      <c r="DS9" s="3" t="inlineStr"/>
+      <c r="DT9" s="3" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="DU9" s="3" t="inlineStr"/>
+      <c r="DV9" s="3" t="inlineStr"/>
+      <c r="DW9" s="3" t="inlineStr"/>
+      <c r="DX9" s="3" t="inlineStr"/>
+      <c r="DY9" s="3" t="inlineStr"/>
+      <c r="DZ9" s="3" t="inlineStr"/>
+      <c r="EA9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>0.0 (0.2)</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>0.5 (0.0)</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>0.8 (0.6)</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr"/>
+      <c r="W10" s="3" t="inlineStr"/>
+      <c r="X10" s="3" t="inlineStr"/>
+      <c r="Y10" s="3" t="inlineStr"/>
+      <c r="Z10" s="3" t="inlineStr"/>
+      <c r="AA10" s="3" t="inlineStr"/>
+      <c r="AB10" s="3" t="inlineStr"/>
+      <c r="AC10" s="3" t="inlineStr"/>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr"/>
+      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AG10" s="3" t="inlineStr"/>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>3.6 (4.4)</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr"/>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>2.8 (2.5)</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr">
+        <is>
+          <t>2.3 (1.9)</t>
+        </is>
+      </c>
+      <c r="AR10" s="3" t="inlineStr"/>
+      <c r="AS10" s="3" t="inlineStr"/>
+      <c r="AT10" s="3" t="inlineStr"/>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr"/>
+      <c r="AW10" s="3" t="inlineStr"/>
+      <c r="AX10" s="3" t="inlineStr"/>
+      <c r="AY10" s="3" t="inlineStr"/>
+      <c r="AZ10" s="3" t="inlineStr"/>
+      <c r="BA10" s="3" t="inlineStr"/>
+      <c r="BB10" s="3" t="inlineStr"/>
+      <c r="BC10" s="3" t="inlineStr"/>
+      <c r="BD10" s="3" t="inlineStr"/>
+      <c r="BE10" s="3" t="inlineStr"/>
+      <c r="BF10" s="3" t="inlineStr"/>
+      <c r="BG10" s="3" t="inlineStr"/>
+      <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr">
+        <is>
+          <t>4.4 (4.4)</t>
+        </is>
+      </c>
+      <c r="BJ10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr"/>
+      <c r="BL10" s="3" t="inlineStr"/>
+      <c r="BM10" s="3" t="inlineStr">
+        <is>
+          <t>4.7 (4.8)</t>
+        </is>
+      </c>
+      <c r="BN10" s="3" t="inlineStr"/>
+      <c r="BO10" s="3" t="inlineStr"/>
+      <c r="BP10" s="3" t="inlineStr"/>
+      <c r="BQ10" s="3" t="inlineStr">
+        <is>
+          <t>4.9 (5.0)</t>
+        </is>
+      </c>
+      <c r="BR10" s="3" t="inlineStr"/>
+      <c r="BS10" s="3" t="inlineStr"/>
+      <c r="BT10" s="3" t="inlineStr"/>
+      <c r="BU10" s="3" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="BV10" s="3" t="inlineStr"/>
+      <c r="BW10" s="3" t="inlineStr"/>
+      <c r="BX10" s="3" t="inlineStr"/>
+      <c r="BY10" s="3" t="inlineStr"/>
+      <c r="BZ10" s="3" t="inlineStr"/>
+      <c r="CA10" s="3" t="inlineStr"/>
+      <c r="CB10" s="3" t="inlineStr"/>
+      <c r="CC10" s="3" t="inlineStr"/>
+      <c r="CD10" s="3" t="inlineStr"/>
+      <c r="CE10" s="3" t="inlineStr"/>
+      <c r="CF10" s="3" t="inlineStr"/>
+      <c r="CG10" s="3" t="inlineStr"/>
+      <c r="CH10" s="3" t="inlineStr"/>
+      <c r="CI10" s="3" t="inlineStr">
+        <is>
+          <t>-0.25 (-0.25)</t>
+        </is>
+      </c>
+      <c r="CJ10" s="3" t="inlineStr"/>
+      <c r="CK10" s="3" t="inlineStr"/>
+      <c r="CL10" s="3" t="inlineStr"/>
+      <c r="CM10" s="3" t="inlineStr">
+        <is>
+          <t>-0.5 (-1)</t>
+        </is>
+      </c>
+      <c r="CN10" s="3" t="inlineStr"/>
+      <c r="CO10" s="3" t="inlineStr"/>
+      <c r="CP10" s="3" t="inlineStr"/>
+      <c r="CQ10" s="3" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="CR10" s="3" t="inlineStr"/>
+      <c r="CS10" s="3" t="inlineStr"/>
+      <c r="CT10" s="3" t="inlineStr"/>
+      <c r="CU10" s="3" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="CV10" s="3" t="inlineStr"/>
+      <c r="CW10" s="3" t="inlineStr"/>
+      <c r="CX10" s="3" t="inlineStr"/>
+      <c r="CY10" s="3" t="inlineStr"/>
+      <c r="CZ10" s="3" t="inlineStr"/>
+      <c r="DA10" s="3" t="inlineStr"/>
+      <c r="DB10" s="3" t="inlineStr"/>
+      <c r="DC10" s="3" t="inlineStr"/>
+      <c r="DD10" s="3" t="inlineStr"/>
+      <c r="DE10" s="3" t="inlineStr"/>
+      <c r="DF10" s="3" t="inlineStr"/>
+      <c r="DG10" s="3" t="inlineStr"/>
+      <c r="DH10" s="3" t="inlineStr"/>
+      <c r="DI10" s="3" t="inlineStr">
+        <is>
+          <t>5.1 (5.3)</t>
+        </is>
+      </c>
+      <c r="DJ10" s="3" t="inlineStr"/>
+      <c r="DK10" s="3" t="inlineStr"/>
+      <c r="DL10" s="3" t="inlineStr"/>
+      <c r="DM10" s="3" t="inlineStr">
+        <is>
+          <t>3.9 (5.0)</t>
+        </is>
+      </c>
+      <c r="DN10" s="3" t="inlineStr"/>
+      <c r="DO10" s="3" t="inlineStr"/>
+      <c r="DP10" s="3" t="inlineStr"/>
+      <c r="DQ10" s="3" t="inlineStr">
+        <is>
+          <t>3.3 (4.4)</t>
+        </is>
+      </c>
+      <c r="DR10" s="3" t="inlineStr"/>
+      <c r="DS10" s="3" t="inlineStr"/>
+      <c r="DT10" s="3" t="inlineStr"/>
+      <c r="DU10" s="3" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="DV10" s="3" t="inlineStr"/>
+      <c r="DW10" s="3" t="inlineStr"/>
+      <c r="DX10" s="3" t="inlineStr"/>
+      <c r="DY10" s="3" t="inlineStr"/>
+      <c r="DZ10" s="3" t="inlineStr"/>
+      <c r="EA10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>0.2 (0.1)</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>0.9 (0.6)</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>1.2 (1)</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr"/>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr"/>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr"/>
+      <c r="AA11" s="3" t="inlineStr"/>
+      <c r="AB11" s="3" t="inlineStr"/>
+      <c r="AC11" s="3" t="inlineStr"/>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr"/>
+      <c r="AF11" s="3" t="inlineStr"/>
+      <c r="AG11" s="3" t="inlineStr"/>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
+      </c>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr"/>
+      <c r="AM11" s="3" t="inlineStr"/>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>2.6 (2.7)</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr"/>
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>1.9 (2.2)</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr"/>
+      <c r="AT11" s="3" t="inlineStr"/>
+      <c r="AU11" s="3" t="inlineStr"/>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr"/>
+      <c r="AX11" s="3" t="inlineStr"/>
+      <c r="AY11" s="3" t="inlineStr"/>
+      <c r="AZ11" s="3" t="inlineStr"/>
+      <c r="BA11" s="3" t="inlineStr"/>
+      <c r="BB11" s="3" t="inlineStr"/>
+      <c r="BC11" s="3" t="inlineStr"/>
+      <c r="BD11" s="3" t="inlineStr"/>
+      <c r="BE11" s="3" t="inlineStr"/>
+      <c r="BF11" s="3" t="inlineStr"/>
+      <c r="BG11" s="3" t="inlineStr"/>
+      <c r="BH11" s="3" t="inlineStr"/>
+      <c r="BI11" s="3" t="inlineStr"/>
+      <c r="BJ11" s="3" t="inlineStr">
+        <is>
+          <t>4.3 (4.4)</t>
+        </is>
+      </c>
+      <c r="BK11" s="3" t="inlineStr"/>
+      <c r="BL11" s="3" t="inlineStr"/>
+      <c r="BM11" s="3" t="inlineStr"/>
+      <c r="BN11" s="3" t="inlineStr">
+        <is>
+          <t>4.6 (4.8)</t>
+        </is>
+      </c>
+      <c r="BO11" s="3" t="inlineStr"/>
+      <c r="BP11" s="3" t="inlineStr"/>
+      <c r="BQ11" s="3" t="inlineStr"/>
+      <c r="BR11" s="3" t="inlineStr">
+        <is>
+          <t>4.8 (5)</t>
+        </is>
+      </c>
+      <c r="BS11" s="3" t="inlineStr"/>
+      <c r="BT11" s="3" t="inlineStr"/>
+      <c r="BU11" s="3" t="inlineStr"/>
+      <c r="BV11" s="3" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="BW11" s="3" t="inlineStr"/>
+      <c r="BX11" s="3" t="inlineStr"/>
+      <c r="BY11" s="3" t="inlineStr"/>
+      <c r="BZ11" s="3" t="inlineStr"/>
+      <c r="CA11" s="3" t="inlineStr"/>
+      <c r="CB11" s="3" t="inlineStr"/>
+      <c r="CC11" s="3" t="inlineStr"/>
+      <c r="CD11" s="3" t="inlineStr"/>
+      <c r="CE11" s="3" t="inlineStr"/>
+      <c r="CF11" s="3" t="inlineStr"/>
+      <c r="CG11" s="3" t="inlineStr"/>
+      <c r="CH11" s="3" t="inlineStr"/>
+      <c r="CI11" s="3" t="inlineStr"/>
+      <c r="CJ11" s="3" t="inlineStr">
+        <is>
+          <t>-0.25 (-0.25)</t>
+        </is>
+      </c>
+      <c r="CK11" s="3" t="inlineStr"/>
+      <c r="CL11" s="3" t="inlineStr"/>
+      <c r="CM11" s="3" t="inlineStr"/>
+      <c r="CN11" s="3" t="inlineStr">
+        <is>
+          <t>-0.75 (-0.75)</t>
+        </is>
+      </c>
+      <c r="CO11" s="3" t="inlineStr"/>
+      <c r="CP11" s="3" t="inlineStr"/>
+      <c r="CQ11" s="3" t="inlineStr"/>
+      <c r="CR11" s="3" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="CS11" s="3" t="inlineStr"/>
+      <c r="CT11" s="3" t="inlineStr"/>
+      <c r="CU11" s="3" t="inlineStr"/>
+      <c r="CV11" s="3" t="inlineStr">
+        <is>
+          <t>0.25 (-1)</t>
+        </is>
+      </c>
+      <c r="CW11" s="3" t="inlineStr"/>
+      <c r="CX11" s="3" t="inlineStr"/>
+      <c r="CY11" s="3" t="inlineStr"/>
+      <c r="CZ11" s="3" t="inlineStr"/>
+      <c r="DA11" s="3" t="inlineStr"/>
+      <c r="DB11" s="3" t="inlineStr"/>
+      <c r="DC11" s="3" t="inlineStr"/>
+      <c r="DD11" s="3" t="inlineStr"/>
+      <c r="DE11" s="3" t="inlineStr"/>
+      <c r="DF11" s="3" t="inlineStr"/>
+      <c r="DG11" s="3" t="inlineStr"/>
+      <c r="DH11" s="3" t="inlineStr"/>
+      <c r="DI11" s="3" t="inlineStr"/>
+      <c r="DJ11" s="3" t="inlineStr">
+        <is>
+          <t>5.2 (5)</t>
+        </is>
+      </c>
+      <c r="DK11" s="3" t="inlineStr"/>
+      <c r="DL11" s="3" t="inlineStr"/>
+      <c r="DM11" s="3" t="inlineStr"/>
+      <c r="DN11" s="3" t="inlineStr">
+        <is>
+          <t>4.5 (3.7)</t>
+        </is>
+      </c>
+      <c r="DO11" s="3" t="inlineStr"/>
+      <c r="DP11" s="3" t="inlineStr"/>
+      <c r="DQ11" s="3" t="inlineStr"/>
+      <c r="DR11" s="3" t="inlineStr">
+        <is>
+          <t>4 (3.3)</t>
+        </is>
+      </c>
+      <c r="DS11" s="3" t="inlineStr"/>
+      <c r="DT11" s="3" t="inlineStr"/>
+      <c r="DU11" s="3" t="inlineStr"/>
+      <c r="DV11" s="3" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="DW11" s="3" t="inlineStr"/>
+      <c r="DX11" s="3" t="inlineStr"/>
+      <c r="DY11" s="3" t="inlineStr"/>
+      <c r="DZ11" s="3" t="inlineStr"/>
+      <c r="EA11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr"/>
+      <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>1.5 (0.5)</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="inlineStr"/>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>0.8 (0.9)</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr"/>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>1.4 (1.3)</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr"/>
+      <c r="V12" s="3" t="inlineStr"/>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr"/>
+      <c r="Y12" s="3" t="inlineStr"/>
+      <c r="Z12" s="3" t="inlineStr"/>
+      <c r="AA12" s="3" t="inlineStr"/>
+      <c r="AB12" s="3" t="inlineStr"/>
+      <c r="AC12" s="3" t="inlineStr"/>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr"/>
+      <c r="AF12" s="3" t="inlineStr"/>
+      <c r="AG12" s="3" t="inlineStr"/>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr"/>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr">
+        <is>
+          <t>2.3 (2.2)</t>
+        </is>
+      </c>
+      <c r="AL12" s="3" t="inlineStr"/>
+      <c r="AM12" s="3" t="inlineStr"/>
+      <c r="AN12" s="3" t="inlineStr"/>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>2.4 (2.5)</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr"/>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr"/>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>1.7 (1.8)</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr"/>
+      <c r="AU12" s="3" t="inlineStr"/>
+      <c r="AV12" s="3" t="inlineStr"/>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr"/>
+      <c r="AY12" s="3" t="inlineStr"/>
+      <c r="AZ12" s="3" t="inlineStr"/>
+      <c r="BA12" s="3" t="inlineStr"/>
+      <c r="BB12" s="3" t="inlineStr"/>
+      <c r="BC12" s="3" t="inlineStr"/>
+      <c r="BD12" s="3" t="inlineStr"/>
+      <c r="BE12" s="3" t="inlineStr"/>
+      <c r="BF12" s="3" t="inlineStr"/>
+      <c r="BG12" s="3" t="inlineStr"/>
+      <c r="BH12" s="3" t="inlineStr"/>
+      <c r="BI12" s="3" t="inlineStr"/>
+      <c r="BJ12" s="3" t="inlineStr"/>
+      <c r="BK12" s="3" t="inlineStr">
+        <is>
+          <t>4.4 (4.3)</t>
+        </is>
+      </c>
+      <c r="BL12" s="3" t="inlineStr"/>
+      <c r="BM12" s="3" t="inlineStr"/>
+      <c r="BN12" s="3" t="inlineStr"/>
+      <c r="BO12" s="3" t="inlineStr">
+        <is>
+          <t>4.6 (4.7)</t>
+        </is>
+      </c>
+      <c r="BP12" s="3" t="inlineStr"/>
+      <c r="BQ12" s="3" t="inlineStr"/>
+      <c r="BR12" s="3" t="inlineStr"/>
+      <c r="BS12" s="3" t="inlineStr">
+        <is>
+          <t>4.8 (4.9)</t>
+        </is>
+      </c>
+      <c r="BT12" s="3" t="inlineStr"/>
+      <c r="BU12" s="3" t="inlineStr"/>
+      <c r="BV12" s="3" t="inlineStr"/>
+      <c r="BW12" s="3" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="BX12" s="3" t="inlineStr"/>
+      <c r="BY12" s="3" t="inlineStr"/>
+      <c r="BZ12" s="3" t="inlineStr"/>
+      <c r="CA12" s="3" t="inlineStr"/>
+      <c r="CB12" s="3" t="inlineStr"/>
+      <c r="CC12" s="3" t="inlineStr"/>
+      <c r="CD12" s="3" t="inlineStr"/>
+      <c r="CE12" s="3" t="inlineStr"/>
+      <c r="CF12" s="3" t="inlineStr"/>
+      <c r="CG12" s="3" t="inlineStr"/>
+      <c r="CH12" s="3" t="inlineStr"/>
+      <c r="CI12" s="3" t="inlineStr"/>
+      <c r="CJ12" s="3" t="inlineStr"/>
+      <c r="CK12" s="3" t="inlineStr">
+        <is>
+          <t>0 (-0.25)</t>
+        </is>
+      </c>
+      <c r="CL12" s="3" t="inlineStr"/>
+      <c r="CM12" s="3" t="inlineStr"/>
+      <c r="CN12" s="3" t="inlineStr"/>
+      <c r="CO12" s="3" t="inlineStr">
+        <is>
+          <t>-1 (-1)</t>
+        </is>
+      </c>
+      <c r="CP12" s="3" t="inlineStr"/>
+      <c r="CQ12" s="3" t="inlineStr"/>
+      <c r="CR12" s="3" t="inlineStr"/>
+      <c r="CS12" s="3" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="CT12" s="3" t="inlineStr"/>
+      <c r="CU12" s="3" t="inlineStr"/>
+      <c r="CV12" s="3" t="inlineStr"/>
+      <c r="CW12" s="3" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="CX12" s="3" t="inlineStr"/>
+      <c r="CY12" s="3" t="inlineStr"/>
+      <c r="CZ12" s="3" t="inlineStr"/>
+      <c r="DA12" s="3" t="inlineStr"/>
+      <c r="DB12" s="3" t="inlineStr"/>
+      <c r="DC12" s="3" t="inlineStr"/>
+      <c r="DD12" s="3" t="inlineStr"/>
+      <c r="DE12" s="3" t="inlineStr"/>
+      <c r="DF12" s="3" t="inlineStr"/>
+      <c r="DG12" s="3" t="inlineStr"/>
+      <c r="DH12" s="3" t="inlineStr"/>
+      <c r="DI12" s="3" t="inlineStr"/>
+      <c r="DJ12" s="3" t="inlineStr"/>
+      <c r="DK12" s="3" t="inlineStr">
+        <is>
+          <t>5.1 (5.0)</t>
+        </is>
+      </c>
+      <c r="DL12" s="3" t="inlineStr"/>
+      <c r="DM12" s="3" t="inlineStr"/>
+      <c r="DN12" s="3" t="inlineStr"/>
+      <c r="DO12" s="3" t="inlineStr">
+        <is>
+          <t>4.2 (4.4)</t>
+        </is>
+      </c>
+      <c r="DP12" s="3" t="inlineStr"/>
+      <c r="DQ12" s="3" t="inlineStr"/>
+      <c r="DR12" s="3" t="inlineStr"/>
+      <c r="DS12" s="3" t="inlineStr">
+        <is>
+          <t>3.8 (3.9)</t>
+        </is>
+      </c>
+      <c r="DT12" s="3" t="inlineStr"/>
+      <c r="DU12" s="3" t="inlineStr"/>
+      <c r="DV12" s="3" t="inlineStr"/>
+      <c r="DW12" s="3" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="DX12" s="3" t="inlineStr"/>
+      <c r="DY12" s="3" t="inlineStr"/>
+      <c r="DZ12" s="3" t="inlineStr"/>
+      <c r="EA12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>1.7 (2)</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>1.7 (0.9)</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t>1.1 (1.5)</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr"/>
+      <c r="V13" s="3" t="inlineStr"/>
+      <c r="W13" s="3" t="inlineStr"/>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="Z13" s="3" t="inlineStr"/>
+      <c r="AA13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="AC13" s="3" t="inlineStr"/>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr"/>
+      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AG13" s="3" t="inlineStr"/>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr"/>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>2.4 (2.7)</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr"/>
+      <c r="AN13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>2.7 (2.2)</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr"/>
+      <c r="AS13" s="3" t="inlineStr"/>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>2.2 (1.6)</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr"/>
+      <c r="AV13" s="3" t="inlineStr"/>
+      <c r="AW13" s="3" t="inlineStr"/>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="AY13" s="3" t="inlineStr"/>
+      <c r="AZ13" s="3" t="inlineStr"/>
+      <c r="BA13" s="3" t="inlineStr"/>
+      <c r="BB13" s="3" t="inlineStr"/>
+      <c r="BC13" s="3" t="inlineStr"/>
+      <c r="BD13" s="3" t="inlineStr"/>
+      <c r="BE13" s="3" t="inlineStr"/>
+      <c r="BF13" s="3" t="inlineStr"/>
+      <c r="BG13" s="3" t="inlineStr"/>
+      <c r="BH13" s="3" t="inlineStr"/>
+      <c r="BI13" s="3" t="inlineStr"/>
+      <c r="BJ13" s="3" t="inlineStr"/>
+      <c r="BK13" s="3" t="inlineStr"/>
+      <c r="BL13" s="3" t="inlineStr">
+        <is>
+          <t>4.2 (4.4)</t>
+        </is>
+      </c>
+      <c r="BM13" s="3" t="inlineStr"/>
+      <c r="BN13" s="3" t="inlineStr"/>
+      <c r="BO13" s="3" t="inlineStr"/>
+      <c r="BP13" s="3" t="inlineStr">
+        <is>
+          <t>4.1 (4.7)</t>
+        </is>
+      </c>
+      <c r="BQ13" s="3" t="inlineStr"/>
+      <c r="BR13" s="3" t="inlineStr"/>
+      <c r="BS13" s="3" t="inlineStr"/>
+      <c r="BT13" s="3" t="inlineStr">
+        <is>
+          <t>4.3 (4.7)</t>
+        </is>
+      </c>
+      <c r="BU13" s="3" t="inlineStr"/>
+      <c r="BV13" s="3" t="inlineStr"/>
+      <c r="BW13" s="3" t="inlineStr"/>
+      <c r="BX13" s="3" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="BY13" s="3" t="inlineStr"/>
+      <c r="BZ13" s="3" t="inlineStr"/>
+      <c r="CA13" s="3" t="inlineStr"/>
+      <c r="CB13" s="3" t="inlineStr"/>
+      <c r="CC13" s="3" t="inlineStr"/>
+      <c r="CD13" s="3" t="inlineStr"/>
+      <c r="CE13" s="3" t="inlineStr"/>
+      <c r="CF13" s="3" t="inlineStr"/>
+      <c r="CG13" s="3" t="inlineStr"/>
+      <c r="CH13" s="3" t="inlineStr"/>
+      <c r="CI13" s="3" t="inlineStr"/>
+      <c r="CJ13" s="3" t="inlineStr"/>
+      <c r="CK13" s="3" t="inlineStr"/>
+      <c r="CL13" s="3" t="inlineStr">
+        <is>
+          <t>0 (-0.25)</t>
+        </is>
+      </c>
+      <c r="CM13" s="3" t="inlineStr"/>
+      <c r="CN13" s="3" t="inlineStr"/>
+      <c r="CO13" s="3" t="inlineStr"/>
+      <c r="CP13" s="3" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="CQ13" s="3" t="inlineStr"/>
+      <c r="CR13" s="3" t="inlineStr"/>
+      <c r="CS13" s="3" t="inlineStr"/>
+      <c r="CT13" s="3" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="CU13" s="3" t="inlineStr"/>
+      <c r="CV13" s="3" t="inlineStr"/>
+      <c r="CW13" s="3" t="inlineStr"/>
+      <c r="CX13" s="3" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="CY13" s="3" t="inlineStr"/>
+      <c r="CZ13" s="3" t="inlineStr"/>
+      <c r="DA13" s="3" t="inlineStr"/>
+      <c r="DB13" s="3" t="inlineStr"/>
+      <c r="DC13" s="3" t="inlineStr"/>
+      <c r="DD13" s="3" t="inlineStr"/>
+      <c r="DE13" s="3" t="inlineStr"/>
+      <c r="DF13" s="3" t="inlineStr"/>
+      <c r="DG13" s="3" t="inlineStr"/>
+      <c r="DH13" s="3" t="inlineStr"/>
+      <c r="DI13" s="3" t="inlineStr"/>
+      <c r="DJ13" s="3" t="inlineStr"/>
+      <c r="DK13" s="3" t="inlineStr"/>
+      <c r="DL13" s="3" t="inlineStr">
+        <is>
+          <t>4.8 (4.9)</t>
+        </is>
+      </c>
+      <c r="DM13" s="3" t="inlineStr"/>
+      <c r="DN13" s="3" t="inlineStr"/>
+      <c r="DO13" s="3" t="inlineStr"/>
+      <c r="DP13" s="3" t="inlineStr">
+        <is>
+          <t>3.7 (4.1)</t>
+        </is>
+      </c>
+      <c r="DQ13" s="3" t="inlineStr"/>
+      <c r="DR13" s="3" t="inlineStr"/>
+      <c r="DS13" s="3" t="inlineStr"/>
+      <c r="DT13" s="3" t="inlineStr">
+        <is>
+          <t>3.7 (3.7)</t>
+        </is>
+      </c>
+      <c r="DU13" s="3" t="inlineStr"/>
+      <c r="DV13" s="3" t="inlineStr"/>
+      <c r="DW13" s="3" t="inlineStr"/>
+      <c r="DX13" s="3" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="DY13" s="3" t="inlineStr"/>
+      <c r="DZ13" s="3" t="inlineStr"/>
+      <c r="EA13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr"/>
+      <c r="D14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr"/>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>0.4 (1.4)</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>1.5 (1.6)</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>1.3 (1.1)</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr"/>
+      <c r="W14" s="3" t="inlineStr"/>
+      <c r="X14" s="3" t="inlineStr"/>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr"/>
+      <c r="AA14" s="3" t="inlineStr"/>
+      <c r="AB14" s="3" t="inlineStr"/>
+      <c r="AC14" s="3" t="inlineStr"/>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr"/>
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr"/>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr"/>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>2.8 (2.4)</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr"/>
+      <c r="AO14" s="3" t="inlineStr"/>
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr">
+        <is>
+          <t>3 (2.6)</t>
+        </is>
+      </c>
+      <c r="AR14" s="3" t="inlineStr"/>
+      <c r="AS14" s="3" t="inlineStr"/>
+      <c r="AT14" s="3" t="inlineStr"/>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>2.3 (2.1)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr"/>
+      <c r="AW14" s="3" t="inlineStr"/>
+      <c r="AX14" s="3" t="inlineStr"/>
+      <c r="AY14" s="3" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="AZ14" s="3" t="inlineStr"/>
+      <c r="BA14" s="3" t="inlineStr"/>
+      <c r="BB14" s="3" t="inlineStr"/>
+      <c r="BC14" s="3" t="inlineStr"/>
+      <c r="BD14" s="3" t="inlineStr"/>
+      <c r="BE14" s="3" t="inlineStr"/>
+      <c r="BF14" s="3" t="inlineStr"/>
+      <c r="BG14" s="3" t="inlineStr"/>
+      <c r="BH14" s="3" t="inlineStr"/>
+      <c r="BI14" s="3" t="inlineStr"/>
+      <c r="BJ14" s="3" t="inlineStr"/>
+      <c r="BK14" s="3" t="inlineStr"/>
+      <c r="BL14" s="3" t="inlineStr"/>
+      <c r="BM14" s="3" t="inlineStr">
+        <is>
+          <t>4.5 (4.1)</t>
+        </is>
+      </c>
+      <c r="BN14" s="3" t="inlineStr"/>
+      <c r="BO14" s="3" t="inlineStr"/>
+      <c r="BP14" s="3" t="inlineStr"/>
+      <c r="BQ14" s="3" t="inlineStr">
+        <is>
+          <t>4.5 (4.2)</t>
+        </is>
+      </c>
+      <c r="BR14" s="3" t="inlineStr"/>
+      <c r="BS14" s="3" t="inlineStr"/>
+      <c r="BT14" s="3" t="inlineStr"/>
+      <c r="BU14" s="3" t="inlineStr">
+        <is>
+          <t>4.8 (4.3)</t>
+        </is>
+      </c>
+      <c r="BV14" s="3" t="inlineStr"/>
+      <c r="BW14" s="3" t="inlineStr"/>
+      <c r="BX14" s="3" t="inlineStr"/>
+      <c r="BY14" s="3" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="BZ14" s="3" t="inlineStr"/>
+      <c r="CA14" s="3" t="inlineStr"/>
+      <c r="CB14" s="3" t="inlineStr"/>
+      <c r="CC14" s="3" t="inlineStr"/>
+      <c r="CD14" s="3" t="inlineStr"/>
+      <c r="CE14" s="3" t="inlineStr"/>
+      <c r="CF14" s="3" t="inlineStr"/>
+      <c r="CG14" s="3" t="inlineStr"/>
+      <c r="CH14" s="3" t="inlineStr"/>
+      <c r="CI14" s="3" t="inlineStr"/>
+      <c r="CJ14" s="3" t="inlineStr"/>
+      <c r="CK14" s="3" t="inlineStr"/>
+      <c r="CL14" s="3" t="inlineStr"/>
+      <c r="CM14" s="3" t="inlineStr">
+        <is>
+          <t>-0.25 (0)</t>
+        </is>
+      </c>
+      <c r="CN14" s="3" t="inlineStr"/>
+      <c r="CO14" s="3" t="inlineStr"/>
+      <c r="CP14" s="3" t="inlineStr"/>
+      <c r="CQ14" s="3" t="inlineStr">
+        <is>
+          <t>-0.5 (-0.25)</t>
+        </is>
+      </c>
+      <c r="CR14" s="3" t="inlineStr"/>
+      <c r="CS14" s="3" t="inlineStr"/>
+      <c r="CT14" s="3" t="inlineStr"/>
+      <c r="CU14" s="3" t="inlineStr">
+        <is>
+          <t>-0.75 (-0.5)</t>
+        </is>
+      </c>
+      <c r="CV14" s="3" t="inlineStr"/>
+      <c r="CW14" s="3" t="inlineStr"/>
+      <c r="CX14" s="3" t="inlineStr"/>
+      <c r="CY14" s="3" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="CZ14" s="3" t="inlineStr"/>
+      <c r="DA14" s="3" t="inlineStr"/>
+      <c r="DB14" s="3" t="inlineStr"/>
+      <c r="DC14" s="3" t="inlineStr"/>
+      <c r="DD14" s="3" t="inlineStr"/>
+      <c r="DE14" s="3" t="inlineStr"/>
+      <c r="DF14" s="3" t="inlineStr"/>
+      <c r="DG14" s="3" t="inlineStr"/>
+      <c r="DH14" s="3" t="inlineStr"/>
+      <c r="DI14" s="3" t="inlineStr"/>
+      <c r="DJ14" s="3" t="inlineStr"/>
+      <c r="DK14" s="3" t="inlineStr"/>
+      <c r="DL14" s="3" t="inlineStr"/>
+      <c r="DM14" s="3" t="inlineStr">
+        <is>
+          <t>4.6 (4.4)</t>
+        </is>
+      </c>
+      <c r="DN14" s="3" t="inlineStr"/>
+      <c r="DO14" s="3" t="inlineStr"/>
+      <c r="DP14" s="3" t="inlineStr"/>
+      <c r="DQ14" s="3" t="inlineStr">
+        <is>
+          <t>4.2 (3.7)</t>
+        </is>
+      </c>
+      <c r="DR14" s="3" t="inlineStr"/>
+      <c r="DS14" s="3" t="inlineStr"/>
+      <c r="DT14" s="3" t="inlineStr"/>
+      <c r="DU14" s="3" t="inlineStr">
+        <is>
+          <t>4.1 (3.6)</t>
+        </is>
+      </c>
+      <c r="DV14" s="3" t="inlineStr"/>
+      <c r="DW14" s="3" t="inlineStr"/>
+      <c r="DX14" s="3" t="inlineStr"/>
+      <c r="DY14" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="DZ14" s="3" t="inlineStr"/>
+      <c r="EA14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>1.4 (1.5)</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t>1.4 (1.3)</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr"/>
+      <c r="V15" s="3" t="inlineStr"/>
+      <c r="W15" s="3" t="inlineStr"/>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>1.7 (1.6)</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr"/>
+      <c r="AB15" s="3" t="inlineStr"/>
+      <c r="AC15" s="3" t="inlineStr"/>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr"/>
+      <c r="AF15" s="3" t="inlineStr"/>
+      <c r="AG15" s="3" t="inlineStr"/>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr"/>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr"/>
+      <c r="AM15" s="3" t="inlineStr"/>
+      <c r="AN15" s="3" t="inlineStr"/>
+      <c r="AO15" s="3" t="inlineStr"/>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>3.5 (3.6)</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr"/>
+      <c r="AS15" s="3" t="inlineStr"/>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>2.5 (2.5)</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr"/>
+      <c r="AV15" s="3" t="inlineStr"/>
+      <c r="AW15" s="3" t="inlineStr"/>
+      <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
+      </c>
+      <c r="AY15" s="3" t="inlineStr"/>
+      <c r="AZ15" s="3" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="BA15" s="3" t="inlineStr"/>
+      <c r="BB15" s="3" t="inlineStr"/>
+      <c r="BC15" s="3" t="inlineStr"/>
+      <c r="BD15" s="3" t="inlineStr"/>
+      <c r="BE15" s="3" t="inlineStr"/>
+      <c r="BF15" s="3" t="inlineStr"/>
+      <c r="BG15" s="3" t="inlineStr"/>
+      <c r="BH15" s="3" t="inlineStr"/>
+      <c r="BI15" s="3" t="inlineStr"/>
+      <c r="BJ15" s="3" t="inlineStr"/>
+      <c r="BK15" s="3" t="inlineStr"/>
+      <c r="BL15" s="3" t="inlineStr"/>
+      <c r="BM15" s="3" t="inlineStr"/>
+      <c r="BN15" s="3" t="inlineStr"/>
+      <c r="BO15" s="3" t="inlineStr"/>
+      <c r="BP15" s="3" t="inlineStr">
+        <is>
+          <t>5 (4.9)</t>
+        </is>
+      </c>
+      <c r="BQ15" s="3" t="inlineStr"/>
+      <c r="BR15" s="3" t="inlineStr"/>
+      <c r="BS15" s="3" t="inlineStr"/>
+      <c r="BT15" s="3" t="inlineStr">
+        <is>
+          <t>5 (4.9)</t>
+        </is>
+      </c>
+      <c r="BU15" s="3" t="inlineStr"/>
+      <c r="BV15" s="3" t="inlineStr"/>
+      <c r="BW15" s="3" t="inlineStr"/>
+      <c r="BX15" s="3" t="inlineStr">
+        <is>
+          <t>4.9 (4.8)</t>
+        </is>
+      </c>
+      <c r="BY15" s="3" t="inlineStr"/>
+      <c r="BZ15" s="3" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="CA15" s="3" t="inlineStr"/>
+      <c r="CB15" s="3" t="inlineStr"/>
+      <c r="CC15" s="3" t="inlineStr"/>
+      <c r="CD15" s="3" t="inlineStr"/>
+      <c r="CE15" s="3" t="inlineStr"/>
+      <c r="CF15" s="3" t="inlineStr"/>
+      <c r="CG15" s="3" t="inlineStr"/>
+      <c r="CH15" s="3" t="inlineStr"/>
+      <c r="CI15" s="3" t="inlineStr"/>
+      <c r="CJ15" s="3" t="inlineStr"/>
+      <c r="CK15" s="3" t="inlineStr"/>
+      <c r="CL15" s="3" t="inlineStr"/>
+      <c r="CM15" s="3" t="inlineStr"/>
+      <c r="CN15" s="3" t="inlineStr"/>
+      <c r="CO15" s="3" t="inlineStr"/>
+      <c r="CP15" s="3" t="inlineStr">
+        <is>
+          <t>-0.8 (-0.6)</t>
+        </is>
+      </c>
+      <c r="CQ15" s="3" t="inlineStr"/>
+      <c r="CR15" s="3" t="inlineStr"/>
+      <c r="CS15" s="3" t="inlineStr"/>
+      <c r="CT15" s="3" t="inlineStr">
+        <is>
+          <t>-0.7 (-0.6)</t>
+        </is>
+      </c>
+      <c r="CU15" s="3" t="inlineStr"/>
+      <c r="CV15" s="3" t="inlineStr"/>
+      <c r="CW15" s="3" t="inlineStr"/>
+      <c r="CX15" s="3" t="inlineStr">
+        <is>
+          <t>-0.4 (-0.3)</t>
+        </is>
+      </c>
+      <c r="CY15" s="3" t="inlineStr"/>
+      <c r="CZ15" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DA15" s="3" t="inlineStr"/>
+      <c r="DB15" s="3" t="inlineStr"/>
+      <c r="DC15" s="3" t="inlineStr"/>
+      <c r="DD15" s="3" t="inlineStr"/>
+      <c r="DE15" s="3" t="inlineStr"/>
+      <c r="DF15" s="3" t="inlineStr"/>
+      <c r="DG15" s="3" t="inlineStr"/>
+      <c r="DH15" s="3" t="inlineStr"/>
+      <c r="DI15" s="3" t="inlineStr"/>
+      <c r="DJ15" s="3" t="inlineStr"/>
+      <c r="DK15" s="3" t="inlineStr"/>
+      <c r="DL15" s="3" t="inlineStr"/>
+      <c r="DM15" s="3" t="inlineStr"/>
+      <c r="DN15" s="3" t="inlineStr"/>
+      <c r="DO15" s="3" t="inlineStr"/>
+      <c r="DP15" s="3" t="inlineStr">
+        <is>
+          <t>3.9 (3.8)</t>
+        </is>
+      </c>
+      <c r="DQ15" s="3" t="inlineStr"/>
+      <c r="DR15" s="3" t="inlineStr"/>
+      <c r="DS15" s="3" t="inlineStr"/>
+      <c r="DT15" s="3" t="inlineStr">
+        <is>
+          <t>3.5 (3.5)</t>
+        </is>
+      </c>
+      <c r="DU15" s="3" t="inlineStr"/>
+      <c r="DV15" s="3" t="inlineStr"/>
+      <c r="DW15" s="3" t="inlineStr"/>
+      <c r="DX15" s="3" t="inlineStr">
+        <is>
+          <t>3.5 (3.6)</t>
+        </is>
+      </c>
+      <c r="DY15" s="3" t="inlineStr"/>
+      <c r="DZ15" s="3" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="EA15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="inlineStr"/>
+      <c r="D16" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr"/>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr"/>
+      <c r="O16" s="3" t="inlineStr"/>
+      <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>0.8 (1.1)</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>1.2 (1.5)</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr"/>
+      <c r="W16" s="3" t="inlineStr"/>
+      <c r="X16" s="3" t="inlineStr"/>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>1.9 (1.8)</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr"/>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr"/>
+      <c r="AC16" s="3" t="inlineStr"/>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr"/>
+      <c r="AF16" s="3" t="inlineStr"/>
+      <c r="AG16" s="3" t="inlineStr"/>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr"/>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr"/>
+      <c r="AM16" s="3" t="inlineStr"/>
+      <c r="AN16" s="3" t="inlineStr"/>
+      <c r="AO16" s="3" t="inlineStr"/>
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr">
+        <is>
+          <t>3.0 (3.1)</t>
+        </is>
+      </c>
+      <c r="AR16" s="3" t="inlineStr"/>
+      <c r="AS16" s="3" t="inlineStr"/>
+      <c r="AT16" s="3" t="inlineStr"/>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>1.7 (2.2)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr"/>
+      <c r="AW16" s="3" t="inlineStr"/>
+      <c r="AX16" s="3" t="inlineStr"/>
+      <c r="AY16" s="3" t="inlineStr">
+        <is>
+          <t>1.8 (2.1)</t>
+        </is>
+      </c>
+      <c r="AZ16" s="3" t="inlineStr"/>
+      <c r="BA16" s="3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="BB16" s="3" t="inlineStr"/>
+      <c r="BC16" s="3" t="inlineStr"/>
+      <c r="BD16" s="3" t="inlineStr"/>
+      <c r="BE16" s="3" t="inlineStr"/>
+      <c r="BF16" s="3" t="inlineStr"/>
+      <c r="BG16" s="3" t="inlineStr"/>
+      <c r="BH16" s="3" t="inlineStr"/>
+      <c r="BI16" s="3" t="inlineStr"/>
+      <c r="BJ16" s="3" t="inlineStr"/>
+      <c r="BK16" s="3" t="inlineStr"/>
+      <c r="BL16" s="3" t="inlineStr"/>
+      <c r="BM16" s="3" t="inlineStr"/>
+      <c r="BN16" s="3" t="inlineStr"/>
+      <c r="BO16" s="3" t="inlineStr"/>
+      <c r="BP16" s="3" t="inlineStr"/>
+      <c r="BQ16" s="3" t="inlineStr">
+        <is>
+          <t>5.2 (5.0)</t>
+        </is>
+      </c>
+      <c r="BR16" s="3" t="inlineStr"/>
+      <c r="BS16" s="3" t="inlineStr"/>
+      <c r="BT16" s="3" t="inlineStr"/>
+      <c r="BU16" s="3" t="inlineStr">
+        <is>
+          <t>5.3 (5.0)</t>
+        </is>
+      </c>
+      <c r="BV16" s="3" t="inlineStr"/>
+      <c r="BW16" s="3" t="inlineStr"/>
+      <c r="BX16" s="3" t="inlineStr"/>
+      <c r="BY16" s="3" t="inlineStr">
+        <is>
+          <t>5.1 (4.9)</t>
+        </is>
+      </c>
+      <c r="BZ16" s="3" t="inlineStr"/>
+      <c r="CA16" s="3" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="CB16" s="3" t="inlineStr"/>
+      <c r="CC16" s="3" t="inlineStr"/>
+      <c r="CD16" s="3" t="inlineStr"/>
+      <c r="CE16" s="3" t="inlineStr"/>
+      <c r="CF16" s="3" t="inlineStr"/>
+      <c r="CG16" s="3" t="inlineStr"/>
+      <c r="CH16" s="3" t="inlineStr"/>
+      <c r="CI16" s="3" t="inlineStr"/>
+      <c r="CJ16" s="3" t="inlineStr"/>
+      <c r="CK16" s="3" t="inlineStr"/>
+      <c r="CL16" s="3" t="inlineStr"/>
+      <c r="CM16" s="3" t="inlineStr"/>
+      <c r="CN16" s="3" t="inlineStr"/>
+      <c r="CO16" s="3" t="inlineStr"/>
+      <c r="CP16" s="3" t="inlineStr"/>
+      <c r="CQ16" s="3" t="inlineStr">
+        <is>
+          <t>-0.9 (-0.8)</t>
+        </is>
+      </c>
+      <c r="CR16" s="3" t="inlineStr"/>
+      <c r="CS16" s="3" t="inlineStr"/>
+      <c r="CT16" s="3" t="inlineStr"/>
+      <c r="CU16" s="3" t="inlineStr">
+        <is>
+          <t>-0.9 (-0.6)</t>
+        </is>
+      </c>
+      <c r="CV16" s="3" t="inlineStr"/>
+      <c r="CW16" s="3" t="inlineStr"/>
+      <c r="CX16" s="3" t="inlineStr"/>
+      <c r="CY16" s="3" t="inlineStr">
+        <is>
+          <t>-0.5 (-0.3)</t>
+        </is>
+      </c>
+      <c r="CZ16" s="3" t="inlineStr"/>
+      <c r="DA16" s="3" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="DB16" s="3" t="inlineStr"/>
+      <c r="DC16" s="3" t="inlineStr"/>
+      <c r="DD16" s="3" t="inlineStr"/>
+      <c r="DE16" s="3" t="inlineStr"/>
+      <c r="DF16" s="3" t="inlineStr"/>
+      <c r="DG16" s="3" t="inlineStr"/>
+      <c r="DH16" s="3" t="inlineStr"/>
+      <c r="DI16" s="3" t="inlineStr"/>
+      <c r="DJ16" s="3" t="inlineStr"/>
+      <c r="DK16" s="3" t="inlineStr"/>
+      <c r="DL16" s="3" t="inlineStr"/>
+      <c r="DM16" s="3" t="inlineStr"/>
+      <c r="DN16" s="3" t="inlineStr"/>
+      <c r="DO16" s="3" t="inlineStr"/>
+      <c r="DP16" s="3" t="inlineStr"/>
+      <c r="DQ16" s="3" t="inlineStr">
+        <is>
+          <t>3.7 (3.8)</t>
+        </is>
+      </c>
+      <c r="DR16" s="3" t="inlineStr"/>
+      <c r="DS16" s="3" t="inlineStr"/>
+      <c r="DT16" s="3" t="inlineStr"/>
+      <c r="DU16" s="3" t="inlineStr">
+        <is>
+          <t>3.3 (3.5)</t>
+        </is>
+      </c>
+      <c r="DV16" s="3" t="inlineStr"/>
+      <c r="DW16" s="3" t="inlineStr"/>
+      <c r="DX16" s="3" t="inlineStr"/>
+      <c r="DY16" s="3" t="inlineStr">
+        <is>
+          <t>3.5 (3.6)</t>
+        </is>
+      </c>
+      <c r="DZ16" s="3" t="inlineStr"/>
+      <c r="EA16" s="3" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>* Bank Rate : chemin implicite par les marchés sur lequel les projections sont conditionnées (la BoE ne prévoit pas sa propre trajectoire de taux).</t>
         </is>
@@ -1003,12 +4238,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="Z1:AE1"/>
-    <mergeCell ref="T1:Y1"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="N1:S1"/>
+    <mergeCell ref="CB1:DA1"/>
+    <mergeCell ref="B1:AA1"/>
+    <mergeCell ref="DB1:EA1"/>
+    <mergeCell ref="AB1:BA1"/>
     <mergeCell ref="A1:A2"/>
+    <mergeCell ref="BB1:CA1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/boe/boe_mpr.xlsx
+++ b/data/boe/boe_mpr.xlsx
@@ -524,11 +524,11 @@
     <col width="10" customWidth="1" min="52" max="52"/>
     <col width="10" customWidth="1" min="53" max="53"/>
     <col width="17" customWidth="1" min="54" max="54"/>
-    <col width="10" customWidth="1" min="55" max="55"/>
-    <col width="10" customWidth="1" min="56" max="56"/>
-    <col width="10" customWidth="1" min="57" max="57"/>
-    <col width="10" customWidth="1" min="58" max="58"/>
-    <col width="10" customWidth="1" min="59" max="59"/>
+    <col width="11" customWidth="1" min="55" max="55"/>
+    <col width="11" customWidth="1" min="56" max="56"/>
+    <col width="11" customWidth="1" min="57" max="57"/>
+    <col width="11" customWidth="1" min="58" max="58"/>
+    <col width="11" customWidth="1" min="59" max="59"/>
     <col width="11" customWidth="1" min="60" max="60"/>
     <col width="11" customWidth="1" min="61" max="61"/>
     <col width="11" customWidth="1" min="62" max="62"/>
@@ -550,26 +550,26 @@
     <col width="10" customWidth="1" min="78" max="78"/>
     <col width="10" customWidth="1" min="79" max="79"/>
     <col width="21" customWidth="1" min="80" max="80"/>
-    <col width="10" customWidth="1" min="81" max="81"/>
+    <col width="13" customWidth="1" min="81" max="81"/>
     <col width="14" customWidth="1" min="82" max="82"/>
     <col width="11" customWidth="1" min="83" max="83"/>
     <col width="14" customWidth="1" min="84" max="84"/>
-    <col width="10" customWidth="1" min="85" max="85"/>
-    <col width="10" customWidth="1" min="86" max="86"/>
+    <col width="14" customWidth="1" min="85" max="85"/>
+    <col width="13" customWidth="1" min="86" max="86"/>
     <col width="15" customWidth="1" min="87" max="87"/>
     <col width="15" customWidth="1" min="88" max="88"/>
     <col width="14" customWidth="1" min="89" max="89"/>
     <col width="15" customWidth="1" min="90" max="90"/>
     <col width="11" customWidth="1" min="91" max="91"/>
     <col width="15" customWidth="1" min="92" max="92"/>
-    <col width="10" customWidth="1" min="93" max="93"/>
-    <col width="13" customWidth="1" min="94" max="94"/>
+    <col width="12" customWidth="1" min="93" max="93"/>
+    <col width="15" customWidth="1" min="94" max="94"/>
     <col width="14" customWidth="1" min="95" max="95"/>
-    <col width="10" customWidth="1" min="96" max="96"/>
-    <col width="11" customWidth="1" min="97" max="97"/>
+    <col width="12" customWidth="1" min="96" max="96"/>
+    <col width="15" customWidth="1" min="97" max="97"/>
     <col width="13" customWidth="1" min="98" max="98"/>
     <col width="14" customWidth="1" min="99" max="99"/>
-    <col width="11" customWidth="1" min="100" max="100"/>
+    <col width="10" customWidth="1" min="100" max="100"/>
     <col width="10" customWidth="1" min="101" max="101"/>
     <col width="13" customWidth="1" min="102" max="102"/>
     <col width="13" customWidth="1" min="103" max="103"/>
@@ -1377,19 +1377,35 @@
       <c r="AY3" s="3" t="inlineStr"/>
       <c r="AZ3" s="3" t="inlineStr"/>
       <c r="BA3" s="3" t="inlineStr"/>
-      <c r="BB3" s="3" t="inlineStr"/>
+      <c r="BB3" s="3" t="inlineStr">
+        <is>
+          <t>3.6 (3.9)</t>
+        </is>
+      </c>
       <c r="BC3" s="3" t="inlineStr"/>
       <c r="BD3" s="3" t="inlineStr"/>
       <c r="BE3" s="3" t="inlineStr"/>
-      <c r="BF3" s="3" t="inlineStr"/>
+      <c r="BF3" s="3" t="inlineStr">
+        <is>
+          <t>3.9 (4.4)</t>
+        </is>
+      </c>
       <c r="BG3" s="3" t="inlineStr"/>
       <c r="BH3" s="3" t="inlineStr"/>
       <c r="BI3" s="3" t="inlineStr"/>
-      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr">
+        <is>
+          <t>4.6 (4.7)</t>
+        </is>
+      </c>
       <c r="BK3" s="3" t="inlineStr"/>
       <c r="BL3" s="3" t="inlineStr"/>
       <c r="BM3" s="3" t="inlineStr"/>
-      <c r="BN3" s="3" t="inlineStr"/>
+      <c r="BN3" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="BO3" s="3" t="inlineStr"/>
       <c r="BP3" s="3" t="inlineStr"/>
       <c r="BQ3" s="3" t="inlineStr"/>
@@ -1413,7 +1429,7 @@
       <c r="CE3" s="3" t="inlineStr"/>
       <c r="CF3" s="3" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-1.25 (-0.5)</t>
         </is>
       </c>
       <c r="CG3" s="3" t="inlineStr"/>
@@ -1421,7 +1437,7 @@
       <c r="CI3" s="3" t="inlineStr"/>
       <c r="CJ3" s="3" t="inlineStr">
         <is>
-          <t>0.25 (-0.5)</t>
+          <t>-1.75 (-0.5)</t>
         </is>
       </c>
       <c r="CK3" s="3" t="inlineStr"/>
@@ -1429,7 +1445,7 @@
       <c r="CM3" s="3" t="inlineStr"/>
       <c r="CN3" s="3" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="CO3" s="3" t="inlineStr"/>
@@ -1579,19 +1595,35 @@
       <c r="AZ4" s="3" t="inlineStr"/>
       <c r="BA4" s="3" t="inlineStr"/>
       <c r="BB4" s="3" t="inlineStr"/>
-      <c r="BC4" s="3" t="inlineStr"/>
+      <c r="BC4" s="3" t="inlineStr">
+        <is>
+          <t>3.7 (3.5)</t>
+        </is>
+      </c>
       <c r="BD4" s="3" t="inlineStr"/>
       <c r="BE4" s="3" t="inlineStr"/>
       <c r="BF4" s="3" t="inlineStr"/>
-      <c r="BG4" s="3" t="inlineStr"/>
+      <c r="BG4" s="3" t="inlineStr">
+        <is>
+          <t>4.4 (4.1)</t>
+        </is>
+      </c>
       <c r="BH4" s="3" t="inlineStr"/>
       <c r="BI4" s="3" t="inlineStr"/>
       <c r="BJ4" s="3" t="inlineStr"/>
-      <c r="BK4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>5.5 (4.8)</t>
+        </is>
+      </c>
       <c r="BL4" s="3" t="inlineStr"/>
       <c r="BM4" s="3" t="inlineStr"/>
       <c r="BN4" s="3" t="inlineStr"/>
-      <c r="BO4" s="3" t="inlineStr"/>
+      <c r="BO4" s="3" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
       <c r="BP4" s="3" t="inlineStr"/>
       <c r="BQ4" s="3" t="inlineStr"/>
       <c r="BR4" s="3" t="inlineStr"/>
@@ -1607,7 +1639,7 @@
       <c r="CB4" s="3" t="inlineStr"/>
       <c r="CC4" s="3" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.75 (0.25)</t>
         </is>
       </c>
       <c r="CD4" s="3" t="inlineStr"/>
@@ -1615,7 +1647,7 @@
       <c r="CF4" s="3" t="inlineStr"/>
       <c r="CG4" s="3" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-2.25 (-1.5)</t>
         </is>
       </c>
       <c r="CH4" s="3" t="inlineStr"/>
@@ -1623,7 +1655,7 @@
       <c r="CJ4" s="3" t="inlineStr"/>
       <c r="CK4" s="3" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3.25 (-2)</t>
         </is>
       </c>
       <c r="CL4" s="3" t="inlineStr"/>
@@ -1631,7 +1663,7 @@
       <c r="CN4" s="3" t="inlineStr"/>
       <c r="CO4" s="3" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="CP4" s="3" t="inlineStr"/>
@@ -1781,19 +1813,35 @@
       <c r="BA5" s="3" t="inlineStr"/>
       <c r="BB5" s="3" t="inlineStr"/>
       <c r="BC5" s="3" t="inlineStr"/>
-      <c r="BD5" s="3" t="inlineStr"/>
+      <c r="BD5" s="3" t="inlineStr">
+        <is>
+          <t>3.7 (3.7)</t>
+        </is>
+      </c>
       <c r="BE5" s="3" t="inlineStr"/>
       <c r="BF5" s="3" t="inlineStr"/>
       <c r="BG5" s="3" t="inlineStr"/>
-      <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BH5" s="3" t="inlineStr">
+        <is>
+          <t>4.9 (4.7)</t>
+        </is>
+      </c>
       <c r="BI5" s="3" t="inlineStr"/>
       <c r="BJ5" s="3" t="inlineStr"/>
       <c r="BK5" s="3" t="inlineStr"/>
-      <c r="BL5" s="3" t="inlineStr"/>
+      <c r="BL5" s="3" t="inlineStr">
+        <is>
+          <t>5.9 (5.7)</t>
+        </is>
+      </c>
       <c r="BM5" s="3" t="inlineStr"/>
       <c r="BN5" s="3" t="inlineStr"/>
       <c r="BO5" s="3" t="inlineStr"/>
-      <c r="BP5" s="3" t="inlineStr"/>
+      <c r="BP5" s="3" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
       <c r="BQ5" s="3" t="inlineStr"/>
       <c r="BR5" s="3" t="inlineStr"/>
       <c r="BS5" s="3" t="inlineStr"/>
@@ -1817,7 +1865,7 @@
       <c r="CG5" s="3" t="inlineStr"/>
       <c r="CH5" s="3" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-2.5 (-2.5)</t>
         </is>
       </c>
       <c r="CI5" s="3" t="inlineStr"/>
@@ -1825,7 +1873,7 @@
       <c r="CK5" s="3" t="inlineStr"/>
       <c r="CL5" s="3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-3 (-3.25)</t>
         </is>
       </c>
       <c r="CM5" s="3" t="inlineStr"/>
@@ -1833,7 +1881,7 @@
       <c r="CO5" s="3" t="inlineStr"/>
       <c r="CP5" s="3" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="CQ5" s="3" t="inlineStr"/>
@@ -1983,19 +2031,35 @@
       <c r="BB6" s="3" t="inlineStr"/>
       <c r="BC6" s="3" t="inlineStr"/>
       <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr"/>
+      <c r="BE6" s="3" t="inlineStr">
+        <is>
+          <t>3.8 (3.8)</t>
+        </is>
+      </c>
       <c r="BF6" s="3" t="inlineStr"/>
       <c r="BG6" s="3" t="inlineStr"/>
       <c r="BH6" s="3" t="inlineStr"/>
-      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr">
+        <is>
+          <t>4.4 (5.2)</t>
+        </is>
+      </c>
       <c r="BJ6" s="3" t="inlineStr"/>
       <c r="BK6" s="3" t="inlineStr"/>
       <c r="BL6" s="3" t="inlineStr"/>
-      <c r="BM6" s="3" t="inlineStr"/>
+      <c r="BM6" s="3" t="inlineStr">
+        <is>
+          <t>5.0 (6.0)</t>
+        </is>
+      </c>
       <c r="BN6" s="3" t="inlineStr"/>
       <c r="BO6" s="3" t="inlineStr"/>
       <c r="BP6" s="3" t="inlineStr"/>
-      <c r="BQ6" s="3" t="inlineStr"/>
+      <c r="BQ6" s="3" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
       <c r="BR6" s="3" t="inlineStr"/>
       <c r="BS6" s="3" t="inlineStr"/>
       <c r="BT6" s="3" t="inlineStr"/>
@@ -2019,7 +2083,7 @@
       <c r="CH6" s="3" t="inlineStr"/>
       <c r="CI6" s="3" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-1.5 (-2.5)</t>
         </is>
       </c>
       <c r="CJ6" s="3" t="inlineStr"/>
@@ -2027,7 +2091,7 @@
       <c r="CL6" s="3" t="inlineStr"/>
       <c r="CM6" s="3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-2 (-3)</t>
         </is>
       </c>
       <c r="CN6" s="3" t="inlineStr"/>
@@ -2185,19 +2249,35 @@
       <c r="BC7" s="3" t="inlineStr"/>
       <c r="BD7" s="3" t="inlineStr"/>
       <c r="BE7" s="3" t="inlineStr"/>
-      <c r="BF7" s="3" t="inlineStr"/>
+      <c r="BF7" s="3" t="inlineStr">
+        <is>
+          <t>3.8 (4.1)</t>
+        </is>
+      </c>
       <c r="BG7" s="3" t="inlineStr"/>
       <c r="BH7" s="3" t="inlineStr"/>
       <c r="BI7" s="3" t="inlineStr"/>
-      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BJ7" s="3" t="inlineStr">
+        <is>
+          <t>3.9 (4.6)</t>
+        </is>
+      </c>
       <c r="BK7" s="3" t="inlineStr"/>
       <c r="BL7" s="3" t="inlineStr"/>
       <c r="BM7" s="3" t="inlineStr"/>
-      <c r="BN7" s="3" t="inlineStr"/>
+      <c r="BN7" s="3" t="inlineStr">
+        <is>
+          <t>4.3 (5.1)</t>
+        </is>
+      </c>
       <c r="BO7" s="3" t="inlineStr"/>
       <c r="BP7" s="3" t="inlineStr"/>
       <c r="BQ7" s="3" t="inlineStr"/>
-      <c r="BR7" s="3" t="inlineStr"/>
+      <c r="BR7" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
       <c r="BS7" s="3" t="inlineStr"/>
       <c r="BT7" s="3" t="inlineStr"/>
       <c r="BU7" s="3" t="inlineStr"/>
@@ -2221,7 +2301,7 @@
       <c r="CI7" s="3" t="inlineStr"/>
       <c r="CJ7" s="3" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.5 (-1.75)</t>
         </is>
       </c>
       <c r="CK7" s="3" t="inlineStr"/>
@@ -2229,7 +2309,7 @@
       <c r="CM7" s="3" t="inlineStr"/>
       <c r="CN7" s="3" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-1 (-2.25)</t>
         </is>
       </c>
       <c r="CO7" s="3" t="inlineStr"/>
@@ -2237,7 +2317,7 @@
       <c r="CQ7" s="3" t="inlineStr"/>
       <c r="CR7" s="3" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="CS7" s="3" t="inlineStr"/>
@@ -2387,19 +2467,35 @@
       <c r="BD8" s="3" t="inlineStr"/>
       <c r="BE8" s="3" t="inlineStr"/>
       <c r="BF8" s="3" t="inlineStr"/>
-      <c r="BG8" s="3" t="inlineStr"/>
+      <c r="BG8" s="3" t="inlineStr">
+        <is>
+          <t>4.1 (3.8)</t>
+        </is>
+      </c>
       <c r="BH8" s="3" t="inlineStr"/>
       <c r="BI8" s="3" t="inlineStr"/>
       <c r="BJ8" s="3" t="inlineStr"/>
-      <c r="BK8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr">
+        <is>
+          <t>4.3 (3.9)</t>
+        </is>
+      </c>
       <c r="BL8" s="3" t="inlineStr"/>
       <c r="BM8" s="3" t="inlineStr"/>
       <c r="BN8" s="3" t="inlineStr"/>
-      <c r="BO8" s="3" t="inlineStr"/>
+      <c r="BO8" s="3" t="inlineStr">
+        <is>
+          <t>4.8 (4.4)</t>
+        </is>
+      </c>
       <c r="BP8" s="3" t="inlineStr"/>
       <c r="BQ8" s="3" t="inlineStr"/>
       <c r="BR8" s="3" t="inlineStr"/>
-      <c r="BS8" s="3" t="inlineStr"/>
+      <c r="BS8" s="3" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
       <c r="BT8" s="3" t="inlineStr"/>
       <c r="BU8" s="3" t="inlineStr"/>
       <c r="BV8" s="3" t="inlineStr"/>
@@ -2431,7 +2527,7 @@
       <c r="CN8" s="3" t="inlineStr"/>
       <c r="CO8" s="3" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-1.25 (-1)</t>
         </is>
       </c>
       <c r="CP8" s="3" t="inlineStr"/>
@@ -2439,7 +2535,7 @@
       <c r="CR8" s="3" t="inlineStr"/>
       <c r="CS8" s="3" t="inlineStr">
         <is>
-          <t>0.25 (-1)</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="CT8" s="3" t="inlineStr"/>
@@ -2649,7 +2745,7 @@
       <c r="CO9" s="3" t="inlineStr"/>
       <c r="CP9" s="3" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-1.5 (-1.5)</t>
         </is>
       </c>
       <c r="CQ9" s="3" t="inlineStr"/>
@@ -2657,7 +2753,7 @@
       <c r="CS9" s="3" t="inlineStr"/>
       <c r="CT9" s="3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="CU9" s="3" t="inlineStr"/>
@@ -2867,7 +2963,7 @@
       <c r="CP10" s="3" t="inlineStr"/>
       <c r="CQ10" s="3" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-1 (-1.5)</t>
         </is>
       </c>
       <c r="CR10" s="3" t="inlineStr"/>
@@ -2875,7 +2971,7 @@
       <c r="CT10" s="3" t="inlineStr"/>
       <c r="CU10" s="3" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="CV10" s="3" t="inlineStr"/>
@@ -3085,7 +3181,7 @@
       <c r="CQ11" s="3" t="inlineStr"/>
       <c r="CR11" s="3" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-1.25 (-1)</t>
         </is>
       </c>
       <c r="CS11" s="3" t="inlineStr"/>
@@ -3093,7 +3189,7 @@
       <c r="CU11" s="3" t="inlineStr"/>
       <c r="CV11" s="3" t="inlineStr">
         <is>
-          <t>0.25 (-1)</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="CW11" s="3" t="inlineStr"/>
@@ -3303,7 +3399,7 @@
       <c r="CR12" s="3" t="inlineStr"/>
       <c r="CS12" s="3" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-1.25 (-1.25)</t>
         </is>
       </c>
       <c r="CT12" s="3" t="inlineStr"/>
@@ -3311,7 +3407,7 @@
       <c r="CV12" s="3" t="inlineStr"/>
       <c r="CW12" s="3" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="CX12" s="3" t="inlineStr"/>
@@ -3513,7 +3609,7 @@
       <c r="CO13" s="3" t="inlineStr"/>
       <c r="CP13" s="3" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.25 (-1.25)</t>
         </is>
       </c>
       <c r="CQ13" s="3" t="inlineStr"/>
@@ -3521,7 +3617,7 @@
       <c r="CS13" s="3" t="inlineStr"/>
       <c r="CT13" s="3" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-0.5 (-1)</t>
         </is>
       </c>
       <c r="CU13" s="3" t="inlineStr"/>
@@ -3529,7 +3625,7 @@
       <c r="CW13" s="3" t="inlineStr"/>
       <c r="CX13" s="3" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="CY13" s="3" t="inlineStr"/>

--- a/data/boe/boe_mpr.xlsx
+++ b/data/boe/boe_mpr.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Résumé (Table 1.A)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Scénarios" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -90,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -102,6 +103,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -467,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2125,15 +2127,69 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="inlineStr"/>
+      <c r="O17" s="3" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr"/>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr"/>
+    </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr"/>
+      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="inlineStr"/>
+      <c r="O18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr"/>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Colonnes alignées par horizon (année en cours, +1, +2, +3), pas par trimestre calendaire : chaque rapport MPR utilise un trimestre de référence différent selon son mois de publication (ex: rapport de février -&gt; Q1, rapport de novembre -&gt; Q4). Le trimestre exact de chaque valeur est rappelé entre crochets.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>* Bank Rate : chemin implicite par les marchés sur lequel les projections sont conditionnées (la BoE ne prévoit pas sa propre trajectoire de taux).</t>
         </is>
@@ -2150,4 +2206,1070 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date du MPR</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Scénario</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Année en cours</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Année +1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Année +2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Année +3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Scenario A</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Inflation IPC</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>[2026 Q2] 3.1</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>[2027 Q2] 2.9</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>[2028 Q2] 1.5</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>[2029 Q2] 1.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Scenario A</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>PIB (glissement annuel)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>[2026 Q2] 0.7</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>[2027 Q2] 0.8</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>[2028 Q2] 1.7</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>[2029 Q2] 1.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Scenario A</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Écart de production</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>[2026 Q2] -1.1</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>[2027 Q2] -1.5</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>[2028 Q2] -1.0</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>[2029 Q2] -0.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Scenario A</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Taux de chômage</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>[2026 Q2] 5.1</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>[2027 Q2] 5.5</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>[2028 Q2] 5.4</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[2029 Q2] 5.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Scenario B</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Inflation IPC</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>[2026 Q2] 3.1</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>[2027 Q2] 3.2</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>[2028 Q2] 2.0</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>[2029 Q2] 2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Scenario B</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>PIB (glissement annuel)</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>[2026 Q2] 0.7</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>[2027 Q2] 0.8</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>[2028 Q2] 1.7</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>[2029 Q2] 1.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Scenario B</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Écart de production</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>[2026 Q2] -1.1</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>[2027 Q2] -1.4</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>[2028 Q2] -1.0</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>[2029 Q2] -0.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Scenario B</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Taux de chômage</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>[2026 Q2] 5.1</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>[2027 Q2] 5.5</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>[2028 Q2] 5.4</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>[2029 Q2] 5.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Scenario C</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Inflation IPC</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>[2026 Q2] 3.6</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>[2027 Q2] 5.6</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>[2028 Q2] 2.9</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>[2029 Q2] 2.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Scenario C</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>PIB (glissement annuel)</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>[2026 Q2] 0.7</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>[2027 Q2] 0.5</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>[2028 Q2] 1.7</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>[2029 Q2] 1.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Scenario C</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Écart de production</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>[2026 Q2] -1.1</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>[2027 Q2] -1.7</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>[2028 Q2] -1.3</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>[2029 Q2] -1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Scenario C</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Taux de chômage</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>[2026 Q2] 5.1</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>[2027 Q2] 5.6</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>[2028 Q2] 5.6</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>[2029 Q2] 5.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Adverse scenario</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Inflation IPC</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>[2026 Q3] 3.1</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>[2027 Q3] 4.1</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>[2028 Q3] 2.8</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>[2029 Q3] 2.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Adverse scenario</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>PIB (glissement annuel)</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>[2026 Q3] 1.1</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>[2027 Q3] 0.9</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>[2028 Q3] 1.6</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>[2029 Q3] 1.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Adverse scenario</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Écart de production</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>[2026 Q3] -1.1</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>[2027 Q3] -1.2</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>[2028 Q3] -1.0</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>[2029 Q3] -0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Adverse scenario</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Taux de chômage</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>[2026 Q3] 5.0</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>[2027 Q3] 5.5</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>[2028 Q3] 5.4</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>[2029 Q3] 5.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Adverse scenario</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Bank Rate (implicite marchés)*</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>[2026 Q3] 3.8</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>[2027 Q3] 4.2</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>[2028 Q3] 4.2</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>[2029 Q3] 4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Central projection</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Inflation IPC</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>[2026 Q3] 2.9</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>[2027 Q3] 2.6</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>[2028 Q3] 1.8</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>[2029 Q3] 1.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Central projection</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>PIB (glissement annuel)</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>[2026 Q3] 1.1</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>[2027 Q3] 1.1</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>[2028 Q3] 1.7</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>[2029 Q3] 1.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Central projection</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Écart de production</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>[2026 Q3] -1.1</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>[2027 Q3] -1.0</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>[2028 Q3] -0.7</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>[2029 Q3] -0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Central projection</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Taux de chômage</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>[2026 Q3] 5.0</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>[2027 Q3] 5.3</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>[2028 Q3] 5.2</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>[2029 Q3] 5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Central projection</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Bank Rate (implicite marchés)*</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>[2026 Q3] 3.8</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>[2027 Q3] 4.2</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>[2028 Q3] 4.2</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>[2029 Q3] 4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Milder scenario</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Inflation IPC</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>[2026 Q3] 2.7</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>[2027 Q3] 2.4</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>[2028 Q3] 1.7</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>[2029 Q3] 1.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Milder scenario</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>PIB (glissement annuel)</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>[2026 Q3] 1.1</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>[2027 Q3] 1.1</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>[2028 Q3] 1.6</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>[2029 Q3] 1.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Milder scenario</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Écart de production</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>[2026 Q3] -1.2</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>[2027 Q3] -1.1</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>[2028 Q3] -0.9</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>[2029 Q3] -0.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Milder scenario</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Taux de chômage</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>[2026 Q3] 5.0</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>[2027 Q3] 5.5</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>[2028 Q3] 5.3</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>[2029 Q3] 5.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Milder scenario</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Bank Rate (implicite marchés)*</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>[2026 Q3] 3.8</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>[2027 Q3] 4.2</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>[2028 Q3] 4.2</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>[2029 Q3] 4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Certaines éditions (ex: avril et juillet 2026) présentent plusieurs scénarios au lieu d'une projection centrale unique, tous conditionnés sur le même chemin de Bank Rate implicite par les marchés -- pas de comparaison avec le rapport précédent dans ce format.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>